--- a/data/sxbet/ligas/Primera A/trades.xlsx
+++ b/data/sxbet/ligas/Primera A/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,102 +531,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>60.05998</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.7575</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CDP Junior FC vs Millonarios</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>CDP Junior FC</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19606649</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1.6637</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Llaneros FC</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>L19614187</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785344668</t>
+          <t>1785400533</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785633300</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.506591</t>
+          <t>79.287102</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,110 +635,222 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.6637</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1785344668</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>1.506591</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>0xb99da8b648376c357d13a6060e6f4dc2ae7491c558b543e4c668392cdfe2e5bd</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.99999</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.6987</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Primera A</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Deportivo Pereira</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0xd09cb30bf0c8317660cdcbbfc8ea542253305047aabd0fa7acee0ff117d36274</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>L19596272</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>1785344544</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1785546000</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>1.431113</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera A/trades.xlsx
+++ b/data/sxbet/ligas/Primera A/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
+          <t>0x407971887685061312685cb0b7f5ef9ed6261d2f1b2d1f09c45aa4eae0a05e25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>60.05998</t>
+          <t>3.57999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.7575</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19614187</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785400533</t>
+          <t>1785434777</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>79.287102</t>
+          <t>6.59906</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,102 +635,94 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>60.05998</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.7575</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CDP Junior FC vs Millonarios</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CDP Junior FC</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19606649</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1.6637</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Llaneros FC</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>L19614187</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785344668</t>
+          <t>1785400533</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785633300</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.506591</t>
+          <t>79.287102</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,110 +739,222 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.6637</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1785344668</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>1.506591</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>0xb99da8b648376c357d13a6060e6f4dc2ae7491c558b543e4c668392cdfe2e5bd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.99999</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1.6987</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Primera A</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Deportivo Pereira</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>0xd09cb30bf0c8317660cdcbbfc8ea542253305047aabd0fa7acee0ff117d36274</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>L19596272</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>1785344544</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>1785546000</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>1.431113</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera A/trades.xlsx
+++ b/data/sxbet/ligas/Primera A/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,18 +531,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x407971887685061312685cb0b7f5ef9ed6261d2f1b2d1f09c45aa4eae0a05e25</t>
+          <t>0x767f70e59b8e41cdfebda1051f2fa906a012de9bfa55942c59f4f2146ac6192f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x1ea5530Db70D5dA696cC1038be611Be53Db5C60F</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.57999</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785434777</t>
+          <t>1785440016</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>6.59906</t>
+          <t>444.239631</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
+          <t>0x407971887685061312685cb0b7f5ef9ed6261d2f1b2d1f09c45aa4eae0a05e25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>60.05998</t>
+          <t>3.57999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.7575</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -667,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19614187</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785400533</t>
+          <t>1785434777</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>79.287102</t>
+          <t>6.59906</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,102 +739,94 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>60.05998</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.7575</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CDP Junior FC vs Millonarios</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CDP Junior FC</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19606649</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1.6637</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Llaneros FC</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>L19614187</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785344668</t>
+          <t>1785400533</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785633300</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.506591</t>
+          <t>79.287102</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,110 +843,222 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.6637</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1785344668</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>1.506591</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>0xb99da8b648376c357d13a6060e6f4dc2ae7491c558b543e4c668392cdfe2e5bd</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.99999</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1.6987</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Primera A</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Deportivo Pereira</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>0xd09cb30bf0c8317660cdcbbfc8ea542253305047aabd0fa7acee0ff117d36274</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>L19596272</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>1785344544</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>1785546000</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>1.431113</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera A/trades.xlsx
+++ b/data/sxbet/ligas/Primera A/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x767f70e59b8e41cdfebda1051f2fa906a012de9bfa55942c59f4f2146ac6192f</t>
+          <t>0xedba5ec6631e3639ff5145bb305ece20e8b3069364c2fe3934ad13a18e2004f2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x1ea5530Db70D5dA696cC1038be611Be53Db5C60F</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.2725</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785440016</t>
+          <t>1785459663</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>444.239631</t>
+          <t>68.697248</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +643,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x407971887685061312685cb0b7f5ef9ed6261d2f1b2d1f09c45aa4eae0a05e25</t>
+          <t>0xa9091dfd45d7760564c0997da3a60bab168f54643ab31141aca0ab8e9ec81033</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.57999</t>
+          <t>141.53</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -682,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785434777</t>
+          <t>1785459106</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>6.59906</t>
+          <t>288.101781</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +747,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
+          <t>0x70dfc6080b5ce53089fea0fe9e58e8db2d467e73911ac1c24f0e3132eeff93ff</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>60.05998</t>
+          <t>141.53</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.7575</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -771,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19614187</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785400533</t>
+          <t>1785459106</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>79.287102</t>
+          <t>288.101781</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,54 +851,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+          <t>0xda5a2ca0728ab585a3a0a417b6b9bc3201516e60647947d6c517fe5aa3b61048</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.485</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.6637</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Atlético Bucaramanga</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Llaneros FC</t>
@@ -898,7 +898,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785344668</t>
+          <t>1785459011</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.506591</t>
+          <t>13.167513</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,110 +955,4206 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>0x0331bf2d5e4c5647823514fbecd4538f8b83f08eca73864d773e7766b093fb2a</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6.485</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.4925</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1785459011</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>13.167513</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0x7c7ef31eaf86810e695207fb33fbd17c8a9667464f034b54067116201439a051</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.4912</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1785458828</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>13.964377</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0x4bae0ce9888d9df37c25c3bd52c2cef2988011ef9500547215ff3c01a8d9ade3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.4912</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1785458828</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>13.964377</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0xf11827477b399686fb93d667a743105e76379dbd2b6ac26fe365b2efa2755088</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>55.54</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.4912</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1785458766</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>113.058524</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0xf172f33c4c2b23605bea3d982f0b82c718d3cccf29fa086a1fbcefb977260877</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>55.54</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.4912</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1785458765</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>113.058524</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0x770626413b7eb60a07b8e7cb17c67cedae414407b96deb76fd5c4807ea3ab23b</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>35.175</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1785458648</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>71.785714</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x420fca3536f3ce2e4be9cfdac1490c3e4a1c8f41c1bd5b62c154f6949a0250d6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>35.175</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1785458648</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>71.785714</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0xdb01c85c09482b9001bcf21790a6d40494a3a5aaf4f8d5bd2884e25499a54a65</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>12.025</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.4925</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1785458515</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>24.416244</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0x5ecc4ae58c7b78276b0defbe103a322d68a770b3df079f300e5c69c2b4731021</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>12.025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.4925</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1785458515</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>24.416244</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0xec7f090351108b7b958a5c4fb3783282609cba12a18c5d155c1f5534aef15888</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1440.5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.4912</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1785458317</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2932.315522</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0xd8cf4f50c442be3b22b3347558a79fd346b09cc1ef8e9b148523105c1d6f374a</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1440.5</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.4912</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1785458316</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2932.315522</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0x6227261e94b21a2814a481af754aa21193c650ab023cebd08d07fdd92c227638</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>56.97</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.2725</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1785457967</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>209.06422</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0xe210f9e86e0bb9e0dd548ab19bdfc825697ddbd94a1f44c6b09e392508136305</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>33.88744</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.7075</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1785457812</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>47.897442</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0x357158ee54a7261c9a3de5193f26c50059ecf3942905b81e23da928f3597b963</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>310.405</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.495</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1785457812</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>627.080808</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0x07d4c22db9e039aaab83659c51b2c610ff2420310c4aa2f6fa5ee9aaa5df5738</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>310.405</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.495</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1785457812</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>627.080808</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0x965925cb75ca17bc44d1270de6e7856136b50e2ba8df869b8ba43a9edfa8cd2c</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>111.49999</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.485</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1785457798</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>229.896887</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0x11cdcc8f35a6869fb42fc42979f00e55e1793e1eaf537612d53ad40413422d94</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>111.49999</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.485</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1785457797</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>229.896887</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0xb08a5fa81a7996a995791b3f412a72d7c00869095f73062c91c21ec7d19936a7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.485</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1785457480</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>459.793814</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0xcd0842e0ce38af317ba18078937aa447779373f330d888eda16082ee857c491b</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.485</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1785457479</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>459.793814</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0x298fa2b8022c9fc657efcae03bbf1c76286c06ada5e405c0b8c01f690927ea9d</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>280.25</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.485</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1785457343</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>577.835052</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0x849609d6471964d5175246b6bc924306468693f7d1aec2da18390bda2d54e0ad</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>280.25</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.485</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1785457342</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>577.835052</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0xbb37e766b7f859769dd38edd2c0b7223eed00c663e6d49a7bfab098f486c206b</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.485</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1785457307</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>309.278351</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0x8f0dbefc5a409af568cf2a038c3e5e0195adaae1692daaf1ec7d82108ff43db8</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.485</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1785457307</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>309.278351</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0x9b20bc474ab348aac134c9be069f670928a6c80a3155e27f3467f12716165c53</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.4875</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1785457201</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>510.769231</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0x3dda88350d6105418404aee1ac185f1858e87b0aba5134695793d721acf1d81d</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.4875</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1785457201</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>510.769231</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0xee9612e6509257c9ad940ec42c374586652e12c5853e386c48508431fbe76d05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.4875</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1785456804</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>307.692308</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0x6ba83cbce2c597c47ad2be6ba26f984375bb5e0a7536df8e0c8b906cdd3cf4b5</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.4875</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1785456804</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>307.692308</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0x8fd96b8c3d361ca4f5d4c858af827e49ded210592392fcd9b074b2a925deaca5</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>17.52</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1785456147</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>58.890756</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x0d8a3334c7809cd2635630f68c141dd8605f414e3fbfb296be4eac2929105fda</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>17.52</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1785456119</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>58.890756</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0xda8af1defc8a29c16e0370161d4a270c766a68fd83aaaeabab9e4378a0673c8d</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>14.76</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1785456113</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>36.9</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0x6455a52d539e6161d9660f2b64423ad8c44b72329f3184934b7abf12459e522b</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1785456018</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>5.333333</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0xf8952a0d91c993a93b0aa47a324ed3d061daa3d53d2a7d88bb539b259c373f92</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1785456003</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>5.209877</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0x999afcdc39345ad0d2e993258d3826f21e43481b2950dcb0f638f2992ac4e4f6</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.9244</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1785454208</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2.88875</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0xf482d08d1fd572eed4c342d8ff10a66ebe3280fdda896e40e465f342e911ccd5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>12.52</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.3125</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1785454207</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>40.064</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0xee4006c4eddaff028b23356cb7de9590b5936ce913b2d1805c50154d5126e6e0</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.3125</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1785454207</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0x767f70e59b8e41cdfebda1051f2fa906a012de9bfa55942c59f4f2146ac6192f</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0x1ea5530Db70D5dA696cC1038be611Be53Db5C60F</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.5425</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1785440016</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>444.239631</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0x407971887685061312685cb0b7f5ef9ed6261d2f1b2d1f09c45aa4eae0a05e25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3.57999</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.5425</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1785434777</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>6.59906</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>60.05998</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.7575</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>CDP Junior FC vs Millonarios</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>CDP Junior FC</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19606649</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1785400533</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1785633300</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>79.287102</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.6637</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1785344668</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1.506591</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>0xb99da8b648376c357d13a6060e6f4dc2ae7491c558b543e4c668392cdfe2e5bd</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>0.99999</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>1.6987</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Primera A</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Deportivo Pereira</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>0xd09cb30bf0c8317660cdcbbfc8ea542253305047aabd0fa7acee0ff117d36274</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>L19596272</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
         <is>
           <t>1785344544</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>1785546000</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>1.431113</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera A/trades.xlsx
+++ b/data/sxbet/ligas/Primera A/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xedba5ec6631e3639ff5145bb305ece20e8b3069364c2fe3934ad13a18e2004f2</t>
+          <t>0x7c7a7beca6e326a985496bfa5683eb5fa550e0b516fd6ce073773eb404203a24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.2725</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Fortaleza CEIF -1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785459663</t>
+          <t>1785508565</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>68.697248</t>
+          <t>2074.074074</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xa9091dfd45d7760564c0997da3a60bab168f54643ab31141aca0ab8e9ec81033</t>
+          <t>0xd193b26f2bd560add82739bdab75d53f792eabeb2448f88b702c3e11effb030c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>141.53</t>
+          <t>999.99999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF -1</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785459106</t>
+          <t>1785508452</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>288.101781</t>
+          <t>1980.198</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,23 +755,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x70dfc6080b5ce53089fea0fe9e58e8db2d467e73911ac1c24f0e3132eeff93ff</t>
+          <t>0xdcff50b650be0657ac4bc1268770ca1b1ea0c65c290a0a114d293e00512af266</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>141.53</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -771,7 +783,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF -1</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -779,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785459106</t>
+          <t>1785508288</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>288.101781</t>
+          <t>597.014925</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,23 +867,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xda5a2ca0728ab585a3a0a417b6b9bc3201516e60647947d6c517fe5aa3b61048</t>
+          <t>0xa40848b46172c1286780eed941c034eeb3a03a4e6390b868015e86a64c340cbf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.485</t>
+          <t>906.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -875,7 +895,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF -1</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -883,27 +907,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785459011</t>
+          <t>1785508285</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13.167513</t>
+          <t>1804.577114</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,31 +979,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x0331bf2d5e4c5647823514fbecd4538f8b83f08eca73864d773e7766b093fb2a</t>
+          <t>0x74b91529e11bc9b801aabc69fc095fca7f0d47339dbee7f0423c6e1fe35b3c56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.485</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF -1</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -987,27 +1019,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1032,17 +1064,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785459011</t>
+          <t>1785508244</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>13.167513</t>
+          <t>597.014925</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,31 +1091,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x7c7ef31eaf86810e695207fb33fbd17c8a9667464f034b54067116201439a051</t>
+          <t>0xedba5ec6631e3639ff5145bb305ece20e8b3069364c2fe3934ad13a18e2004f2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.2725</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -1106,7 +1146,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1136,7 +1176,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785458828</t>
+          <t>1785459663</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1186,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>13.964377</t>
+          <t>68.697248</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,18 +1203,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x4bae0ce9888d9df37c25c3bd52c2cef2988011ef9500547215ff3c01a8d9ade3</t>
+          <t>0xa9091dfd45d7760564c0997da3a60bab168f54643ab31141aca0ab8e9ec81033</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>141.53</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1184,7 +1224,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1210,7 +1250,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1240,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785458828</t>
+          <t>1785459106</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>13.964377</t>
+          <t>288.101781</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,18 +1307,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xf11827477b399686fb93d667a743105e76379dbd2b6ac26fe365b2efa2755088</t>
+          <t>0x70dfc6080b5ce53089fea0fe9e58e8db2d467e73911ac1c24f0e3132eeff93ff</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>55.54</t>
+          <t>141.53</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1344,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785458766</t>
+          <t>1785459106</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1354,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>113.058524</t>
+          <t>288.101781</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,7 +1411,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xf172f33c4c2b23605bea3d982f0b82c718d3cccf29fa086a1fbcefb977260877</t>
+          <t>0xda5a2ca0728ab585a3a0a417b6b9bc3201516e60647947d6c517fe5aa3b61048</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1382,17 +1422,17 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>55.54</t>
+          <t>6.485</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1418,7 +1458,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1448,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785458765</t>
+          <t>1785459011</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1458,7 +1498,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>113.058524</t>
+          <t>13.167513</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,7 +1515,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x770626413b7eb60a07b8e7cb17c67cedae414407b96deb76fd5c4807ea3ab23b</t>
+          <t>0x0331bf2d5e4c5647823514fbecd4538f8b83f08eca73864d773e7766b093fb2a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,12 +1526,12 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>35.175</t>
+          <t>6.485</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1552,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785458648</t>
+          <t>1785459011</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1562,7 +1602,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>71.785714</t>
+          <t>13.167513</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1579,7 +1619,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x420fca3536f3ce2e4be9cfdac1490c3e4a1c8f41c1bd5b62c154f6949a0250d6</t>
+          <t>0x7c7ef31eaf86810e695207fb33fbd17c8a9667464f034b54067116201439a051</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1590,17 +1630,17 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>35.175</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1626,7 +1666,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1656,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785458648</t>
+          <t>1785458828</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1666,7 +1706,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>71.785714</t>
+          <t>13.964377</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1683,7 +1723,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xdb01c85c09482b9001bcf21790a6d40494a3a5aaf4f8d5bd2884e25499a54a65</t>
+          <t>0x4bae0ce9888d9df37c25c3bd52c2cef2988011ef9500547215ff3c01a8d9ade3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1694,17 +1734,17 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12.025</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1730,7 +1770,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1760,7 +1800,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785458515</t>
+          <t>1785458828</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1770,7 +1810,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>24.416244</t>
+          <t>13.964377</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1787,7 +1827,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x5ecc4ae58c7b78276b0defbe103a322d68a770b3df079f300e5c69c2b4731021</t>
+          <t>0xf11827477b399686fb93d667a743105e76379dbd2b6ac26fe365b2efa2755088</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1798,12 +1838,12 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12.025</t>
+          <t>55.54</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1864,7 +1904,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785458515</t>
+          <t>1785458766</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1874,7 +1914,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>24.416244</t>
+          <t>113.058524</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1891,18 +1931,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xec7f090351108b7b958a5c4fb3783282609cba12a18c5d155c1f5534aef15888</t>
+          <t>0xf172f33c4c2b23605bea3d982f0b82c718d3cccf29fa086a1fbcefb977260877</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1440.5</t>
+          <t>55.54</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1912,7 +1952,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1938,7 +1978,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1968,7 +2008,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785458317</t>
+          <t>1785458765</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1978,7 +2018,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2932.315522</t>
+          <t>113.058524</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1995,23 +2035,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xd8cf4f50c442be3b22b3347558a79fd346b09cc1ef8e9b148523105c1d6f374a</t>
+          <t>0x770626413b7eb60a07b8e7cb17c67cedae414407b96deb76fd5c4807ea3ab23b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1440.5</t>
+          <t>35.175</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2072,7 +2112,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785458316</t>
+          <t>1785458648</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2082,7 +2122,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2932.315522</t>
+          <t>71.785714</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2099,39 +2139,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x6227261e94b21a2814a481af754aa21193c650ab023cebd08d07fdd92c227638</t>
+          <t>0x420fca3536f3ce2e4be9cfdac1490c3e4a1c8f41c1bd5b62c154f6949a0250d6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>56.97</t>
+          <t>35.175</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.2725</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -2154,7 +2186,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2184,7 +2216,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785457967</t>
+          <t>1785458648</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2194,7 +2226,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>209.06422</t>
+          <t>71.785714</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2211,7 +2243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xe210f9e86e0bb9e0dd548ab19bdfc825697ddbd94a1f44c6b09e392508136305</t>
+          <t>0xdb01c85c09482b9001bcf21790a6d40494a3a5aaf4f8d5bd2884e25499a54a65</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2222,17 +2254,17 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>33.88744</t>
+          <t>12.025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.7075</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2258,7 +2290,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2288,7 +2320,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785457812</t>
+          <t>1785458515</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2298,7 +2330,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>47.897442</t>
+          <t>24.416244</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2315,7 +2347,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x357158ee54a7261c9a3de5193f26c50059ecf3942905b81e23da928f3597b963</t>
+          <t>0x5ecc4ae58c7b78276b0defbe103a322d68a770b3df079f300e5c69c2b4731021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2326,17 +2358,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>310.405</t>
+          <t>12.025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2362,7 +2394,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2392,7 +2424,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785457812</t>
+          <t>1785458515</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2402,7 +2434,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>627.080808</t>
+          <t>24.416244</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2419,23 +2451,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x07d4c22db9e039aaab83659c51b2c610ff2420310c4aa2f6fa5ee9aaa5df5738</t>
+          <t>0xec7f090351108b7b958a5c4fb3783282609cba12a18c5d155c1f5534aef15888</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>310.405</t>
+          <t>1440.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2496,7 +2528,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785457812</t>
+          <t>1785458317</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2506,7 +2538,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>627.080808</t>
+          <t>2932.315522</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2523,7 +2555,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x965925cb75ca17bc44d1270de6e7856136b50e2ba8df869b8ba43a9edfa8cd2c</t>
+          <t>0xd8cf4f50c442be3b22b3347558a79fd346b09cc1ef8e9b148523105c1d6f374a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2534,17 +2566,17 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>111.49999</t>
+          <t>1440.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2570,7 +2602,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2600,7 +2632,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785457798</t>
+          <t>1785458316</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2610,7 +2642,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>229.896887</t>
+          <t>2932.315522</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2627,31 +2659,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x11cdcc8f35a6869fb42fc42979f00e55e1793e1eaf537612d53ad40413422d94</t>
+          <t>0x6227261e94b21a2814a481af754aa21193c650ab023cebd08d07fdd92c227638</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>111.49999</t>
+          <t>56.97</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.2725</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -2674,7 +2714,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2704,7 +2744,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785457797</t>
+          <t>1785457967</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2714,7 +2754,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>229.896887</t>
+          <t>209.06422</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2731,28 +2771,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xb08a5fa81a7996a995791b3f412a72d7c00869095f73062c91c21ec7d19936a7</t>
+          <t>0xe210f9e86e0bb9e0dd548ab19bdfc825697ddbd94a1f44c6b09e392508136305</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>33.88744</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.7075</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2778,7 +2818,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2808,7 +2848,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785457480</t>
+          <t>1785457812</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2818,7 +2858,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>459.793814</t>
+          <t>47.897442</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2835,23 +2875,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xcd0842e0ce38af317ba18078937aa447779373f330d888eda16082ee857c491b</t>
+          <t>0x357158ee54a7261c9a3de5193f26c50059ecf3942905b81e23da928f3597b963</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>310.405</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2912,7 +2952,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785457479</t>
+          <t>1785457812</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2922,7 +2962,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>459.793814</t>
+          <t>627.080808</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2939,23 +2979,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x298fa2b8022c9fc657efcae03bbf1c76286c06ada5e405c0b8c01f690927ea9d</t>
+          <t>0x07d4c22db9e039aaab83659c51b2c610ff2420310c4aa2f6fa5ee9aaa5df5738</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>280.25</t>
+          <t>310.405</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3016,7 +3056,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785457343</t>
+          <t>1785457812</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3026,7 +3066,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>577.835052</t>
+          <t>627.080808</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3043,18 +3083,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x849609d6471964d5175246b6bc924306468693f7d1aec2da18390bda2d54e0ad</t>
+          <t>0x965925cb75ca17bc44d1270de6e7856136b50e2ba8df869b8ba43a9edfa8cd2c</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>280.25</t>
+          <t>111.49999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3064,7 +3104,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3090,7 +3130,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3120,7 +3160,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785457342</t>
+          <t>1785457798</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3130,7 +3170,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>577.835052</t>
+          <t>229.896887</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3147,18 +3187,18 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xbb37e766b7f859769dd38edd2c0b7223eed00c663e6d49a7bfab098f486c206b</t>
+          <t>0x11cdcc8f35a6869fb42fc42979f00e55e1793e1eaf537612d53ad40413422d94</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>111.49999</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3224,7 +3264,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785457307</t>
+          <t>1785457797</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3234,7 +3274,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>309.278351</t>
+          <t>229.896887</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3251,18 +3291,18 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x8f0dbefc5a409af568cf2a038c3e5e0195adaae1692daaf1ec7d82108ff43db8</t>
+          <t>0xb08a5fa81a7996a995791b3f412a72d7c00869095f73062c91c21ec7d19936a7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3328,7 +3368,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785457307</t>
+          <t>1785457480</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3338,7 +3378,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>309.278351</t>
+          <t>459.793814</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3355,28 +3395,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x9b20bc474ab348aac134c9be069f670928a6c80a3155e27f3467f12716165c53</t>
+          <t>0xcd0842e0ce38af317ba18078937aa447779373f330d888eda16082ee857c491b</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
+          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3402,7 +3442,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3432,7 +3472,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785457201</t>
+          <t>1785457479</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3442,7 +3482,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>510.769231</t>
+          <t>459.793814</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3459,28 +3499,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x3dda88350d6105418404aee1ac185f1858e87b0aba5134695793d721acf1d81d</t>
+          <t>0x298fa2b8022c9fc657efcae03bbf1c76286c06ada5e405c0b8c01f690927ea9d</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>280.25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3506,7 +3546,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3536,7 +3576,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785457201</t>
+          <t>1785457343</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3546,7 +3586,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>510.769231</t>
+          <t>577.835052</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3563,28 +3603,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xee9612e6509257c9ad940ec42c374586652e12c5853e386c48508431fbe76d05</t>
+          <t>0x849609d6471964d5175246b6bc924306468693f7d1aec2da18390bda2d54e0ad</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>280.25</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3610,7 +3650,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3640,7 +3680,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785456804</t>
+          <t>1785457342</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3650,7 +3690,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>307.692308</t>
+          <t>577.835052</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3667,7 +3707,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x6ba83cbce2c597c47ad2be6ba26f984375bb5e0a7536df8e0c8b906cdd3cf4b5</t>
+          <t>0xbb37e766b7f859769dd38edd2c0b7223eed00c663e6d49a7bfab098f486c206b</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3683,7 +3723,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3744,7 +3784,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785456804</t>
+          <t>1785457307</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3754,7 +3794,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>307.692308</t>
+          <t>309.278351</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3771,28 +3811,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x8fd96b8c3d361ca4f5d4c858af827e49ded210592392fcd9b074b2a925deaca5</t>
+          <t>0x8f0dbefc5a409af568cf2a038c3e5e0195adaae1692daaf1ec7d82108ff43db8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3818,7 +3858,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3848,7 +3888,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785456147</t>
+          <t>1785457307</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3858,7 +3898,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>58.890756</t>
+          <t>309.278351</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3875,28 +3915,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x0d8a3334c7809cd2635630f68c141dd8605f414e3fbfb296be4eac2929105fda</t>
+          <t>0x9b20bc474ab348aac134c9be069f670928a6c80a3155e27f3467f12716165c53</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3922,7 +3962,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3952,7 +3992,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785456119</t>
+          <t>1785457201</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3962,7 +4002,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>58.890756</t>
+          <t>510.769231</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -3979,28 +4019,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xda8af1defc8a29c16e0370161d4a270c766a68fd83aaaeabab9e4378a0673c8d</t>
+          <t>0x3dda88350d6105418404aee1ac185f1858e87b0aba5134695793d721acf1d81d</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>14.76</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4026,7 +4066,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4056,7 +4096,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785456113</t>
+          <t>1785457201</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4066,7 +4106,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>510.769231</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4083,28 +4123,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x6455a52d539e6161d9660f2b64423ad8c44b72329f3184934b7abf12459e522b</t>
+          <t>0xee9612e6509257c9ad940ec42c374586652e12c5853e386c48508431fbe76d05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4130,7 +4170,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4160,7 +4200,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785456018</t>
+          <t>1785456804</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4170,7 +4210,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>5.333333</t>
+          <t>307.692308</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4187,28 +4227,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xf8952a0d91c993a93b0aa47a324ed3d061daa3d53d2a7d88bb539b259c373f92</t>
+          <t>0x6ba83cbce2c597c47ad2be6ba26f984375bb5e0a7536df8e0c8b906cdd3cf4b5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4234,7 +4274,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4264,7 +4304,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785456003</t>
+          <t>1785456804</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4274,7 +4314,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>5.209877</t>
+          <t>307.692308</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4291,39 +4331,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x999afcdc39345ad0d2e993258d3826f21e43481b2950dcb0f638f2992ac4e4f6</t>
+          <t>0x8fd96b8c3d361ca4f5d4c858af827e49ded210592392fcd9b074b2a925deaca5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.9244</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -4346,7 +4378,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4376,7 +4408,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785454208</t>
+          <t>1785456147</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4386,7 +4418,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2.88875</t>
+          <t>58.890756</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4403,39 +4435,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xf482d08d1fd572eed4c342d8ff10a66ebe3280fdda896e40e465f342e911ccd5</t>
+          <t>0x0d8a3334c7809cd2635630f68c141dd8605f414e3fbfb296be4eac2929105fda</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -4458,7 +4482,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4488,7 +4512,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785454207</t>
+          <t>1785456119</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4498,7 +4522,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>40.064</t>
+          <t>58.890756</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4515,7 +4539,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xee4006c4eddaff028b23356cb7de9590b5936ce913b2d1805c50154d5126e6e0</t>
+          <t>0xda8af1defc8a29c16e0370161d4a270c766a68fd83aaaeabab9e4378a0673c8d</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4523,31 +4547,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14.76</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -4570,7 +4586,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4600,7 +4616,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785454207</t>
+          <t>1785456113</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4610,7 +4626,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4627,28 +4643,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x767f70e59b8e41cdfebda1051f2fa906a012de9bfa55942c59f4f2146ac6192f</t>
+          <t>0x6455a52d539e6161d9660f2b64423ad8c44b72329f3184934b7abf12459e522b</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x1ea5530Db70D5dA696cC1038be611Be53Db5C60F</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4674,7 +4690,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4704,7 +4720,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785440016</t>
+          <t>1785456018</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4714,7 +4730,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>444.239631</t>
+          <t>5.333333</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4731,7 +4747,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x407971887685061312685cb0b7f5ef9ed6261d2f1b2d1f09c45aa4eae0a05e25</t>
+          <t>0xf8952a0d91c993a93b0aa47a324ed3d061daa3d53d2a7d88bb539b259c373f92</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4742,17 +4758,17 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3.57999</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4778,7 +4794,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4808,7 +4824,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785434777</t>
+          <t>1785456003</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4818,7 +4834,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>6.59906</t>
+          <t>5.209877</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4835,31 +4851,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
+          <t>0x999afcdc39345ad0d2e993258d3826f21e43481b2950dcb0f638f2992ac4e4f6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>60.05998</t>
+          <t>0.9244</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.7575</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -4867,27 +4891,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19614187</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4912,17 +4936,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785400533</t>
+          <t>1785454208</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>79.287102</t>
+          <t>2.88875</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4939,12 +4963,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+          <t>0xf482d08d1fd572eed4c342d8ff10a66ebe3280fdda896e40e465f342e911ccd5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4954,39 +4978,39 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12.52</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.6637</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>Atlético Bucaramanga</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>Llaneros FC</t>
@@ -4994,7 +5018,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5024,7 +5048,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785344668</t>
+          <t>1785454207</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5034,7 +5058,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1.506591</t>
+          <t>40.064</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5051,110 +5075,646 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>0xee4006c4eddaff028b23356cb7de9590b5936ce913b2d1805c50154d5126e6e0</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.3125</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1785454207</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0x767f70e59b8e41cdfebda1051f2fa906a012de9bfa55942c59f4f2146ac6192f</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0x1ea5530Db70D5dA696cC1038be611Be53Db5C60F</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.5425</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1785440016</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>444.239631</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0x407971887685061312685cb0b7f5ef9ed6261d2f1b2d1f09c45aa4eae0a05e25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>3.57999</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.5425</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1785434777</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>6.59906</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>60.05998</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.7575</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>CDP Junior FC vs Millonarios</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>CDP Junior FC</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19606649</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1785400533</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1785633300</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>79.287102</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.6637</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1785344668</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1.506591</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>0xb99da8b648376c357d13a6060e6f4dc2ae7491c558b543e4c668392cdfe2e5bd</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>0.99999</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>1.6987</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Primera A</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Deportivo Pereira</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>0xd09cb30bf0c8317660cdcbbfc8ea542253305047aabd0fa7acee0ff117d36274</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>L19596272</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
         <is>
           <t>1785344544</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>1785546000</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>1.431113</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera A/trades.xlsx
+++ b/data/sxbet/ligas/Primera A/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V50"/>
+  <dimension ref="A1:V53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x7c7a7beca6e326a985496bfa5683eb5fa550e0b516fd6ce073773eb404203a24</t>
+          <t>0x4e6d8aa3987bcfa005261070885a48fd586f27d2bc70935198f0e47d5d57bbc1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.2725</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF -1</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF vs Deportivo Pereira</t>
+          <t>CDP Junior FC vs Millonarios</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>CDP Junior FC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
+          <t>0x99fd85073e61e4ff2811a42fd3c5860bb029aa8bb2842c318e468f64896ecc5e</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19596272</t>
+          <t>L19606649</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785508565</t>
+          <t>1785565485</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785546000</t>
+          <t>1785633300</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2074.074074</t>
+          <t>9.321101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xd193b26f2bd560add82739bdab75d53f792eabeb2448f88b702c3e11effb030c</t>
+          <t>0xa1c75ce4ff8b084ebb89ef9c554b972ba868d695f41f84d5d7eba65ab3bf430e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>999.99999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF -1</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF vs Deportivo Pereira</t>
+          <t>CDP Junior FC vs Millonarios</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>CDP Junior FC</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
+          <t>0x175c82298fd904f82cec6e6df95a6caa5e2925c38ac62b465dc3c16cbe6d7468</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19596272</t>
+          <t>L19606649</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785508452</t>
+          <t>1785565483</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785546000</t>
+          <t>1785633300</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1980.198</t>
+          <t>20.460358</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xdcff50b650be0657ac4bc1268770ca1b1ea0c65c290a0a114d293e00512af266</t>
+          <t>0x804741c7cadd40e1de9b46da558e4f8f76822d01b445af10dcb9b394ea6818b4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,22 +770,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>9.99998</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.7525</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF -1</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF vs Deportivo Pereira</t>
+          <t>CDP Junior FC vs Millonarios</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>CDP Junior FC</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
+          <t>0x3461ee17d707212e3a9027bdc8a10f2a6481bbeefaa491f85e9dad2fc6ef04cd</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19596272</t>
+          <t>L19606649</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785508288</t>
+          <t>1785565483</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785546000</t>
+          <t>1785633300</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>597.014925</t>
+          <t>13.28901</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xa40848b46172c1286780eed941c034eeb3a03a4e6390b868015e86a64c340cbf</t>
+          <t>0x7c7a7beca6e326a985496bfa5683eb5fa550e0b516fd6ce073773eb404203a24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>906.8</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785508285</t>
+          <t>1785508565</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1804.577114</t>
+          <t>2074.074074</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,12 +979,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x74b91529e11bc9b801aabc69fc095fca7f0d47339dbee7f0423c6e1fe35b3c56</t>
+          <t>0xd193b26f2bd560add82739bdab75d53f792eabeb2448f88b702c3e11effb030c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>999.99999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785508244</t>
+          <t>1785508452</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>597.014925</t>
+          <t>1980.198</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,12 +1091,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xedba5ec6631e3639ff5145bb305ece20e8b3069364c2fe3934ad13a18e2004f2</t>
+          <t>0xdcff50b650be0657ac4bc1268770ca1b1ea0c65c290a0a114d293e00512af266</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1106,22 +1106,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2725</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Fortaleza CEIF -1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1131,27 +1131,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785459663</t>
+          <t>1785508288</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>68.697248</t>
+          <t>597.014925</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1203,31 +1203,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xa9091dfd45d7760564c0997da3a60bab168f54643ab31141aca0ab8e9ec81033</t>
+          <t>0xa40848b46172c1286780eed941c034eeb3a03a4e6390b868015e86a64c340cbf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>141.53</t>
+          <t>906.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF -1</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -1235,27 +1243,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1288,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785459106</t>
+          <t>1785508285</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>288.101781</t>
+          <t>1804.577114</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,23 +1315,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x70dfc6080b5ce53089fea0fe9e58e8db2d467e73911ac1c24f0e3132eeff93ff</t>
+          <t>0x74b91529e11bc9b801aabc69fc095fca7f0d47339dbee7f0423c6e1fe35b3c56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>141.53</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1331,7 +1343,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF -1</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -1339,27 +1355,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1384,17 +1400,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785459106</t>
+          <t>1785508244</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>288.101781</t>
+          <t>597.014925</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,31 +1427,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xda5a2ca0728ab585a3a0a417b6b9bc3201516e60647947d6c517fe5aa3b61048</t>
+          <t>0xedba5ec6631e3639ff5145bb305ece20e8b3069364c2fe3934ad13a18e2004f2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.485</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.2725</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -1458,7 +1482,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1488,7 +1512,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785459011</t>
+          <t>1785459663</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1522,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>13.167513</t>
+          <t>68.697248</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,23 +1539,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x0331bf2d5e4c5647823514fbecd4538f8b83f08eca73864d773e7766b093fb2a</t>
+          <t>0xa9091dfd45d7760564c0997da3a60bab168f54643ab31141aca0ab8e9ec81033</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.485</t>
+          <t>141.53</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1592,7 +1616,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785459011</t>
+          <t>1785459106</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1626,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>13.167513</t>
+          <t>288.101781</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,18 +1643,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x7c7ef31eaf86810e695207fb33fbd17c8a9667464f034b54067116201439a051</t>
+          <t>0x70dfc6080b5ce53089fea0fe9e58e8db2d467e73911ac1c24f0e3132eeff93ff</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>141.53</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1640,7 +1664,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1666,7 +1690,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1696,7 +1720,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785458828</t>
+          <t>1785459106</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1706,7 +1730,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>13.964377</t>
+          <t>288.101781</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,7 +1747,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x4bae0ce9888d9df37c25c3bd52c2cef2988011ef9500547215ff3c01a8d9ade3</t>
+          <t>0xda5a2ca0728ab585a3a0a417b6b9bc3201516e60647947d6c517fe5aa3b61048</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1734,12 +1758,12 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>6.485</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1800,7 +1824,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785458828</t>
+          <t>1785459011</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1810,7 +1834,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>13.964377</t>
+          <t>13.167513</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1827,7 +1851,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xf11827477b399686fb93d667a743105e76379dbd2b6ac26fe365b2efa2755088</t>
+          <t>0x0331bf2d5e4c5647823514fbecd4538f8b83f08eca73864d773e7766b093fb2a</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1838,17 +1862,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>55.54</t>
+          <t>6.485</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1874,7 +1898,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1904,7 +1928,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785458766</t>
+          <t>1785459011</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1914,7 +1938,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>113.058524</t>
+          <t>13.167513</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1931,7 +1955,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xf172f33c4c2b23605bea3d982f0b82c718d3cccf29fa086a1fbcefb977260877</t>
+          <t>0x7c7ef31eaf86810e695207fb33fbd17c8a9667464f034b54067116201439a051</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1942,7 +1966,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55.54</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2008,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785458765</t>
+          <t>1785458828</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2018,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>113.058524</t>
+          <t>13.964377</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,7 +2059,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x770626413b7eb60a07b8e7cb17c67cedae414407b96deb76fd5c4807ea3ab23b</t>
+          <t>0x4bae0ce9888d9df37c25c3bd52c2cef2988011ef9500547215ff3c01a8d9ade3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2046,17 +2070,17 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>35.175</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2082,7 +2106,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2112,7 +2136,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785458648</t>
+          <t>1785458828</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2122,7 +2146,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>71.785714</t>
+          <t>13.964377</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,7 +2163,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x420fca3536f3ce2e4be9cfdac1490c3e4a1c8f41c1bd5b62c154f6949a0250d6</t>
+          <t>0xf11827477b399686fb93d667a743105e76379dbd2b6ac26fe365b2efa2755088</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2150,12 +2174,12 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>35.175</t>
+          <t>55.54</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2216,7 +2240,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785458648</t>
+          <t>1785458766</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2226,7 +2250,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>71.785714</t>
+          <t>113.058524</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2243,7 +2267,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xdb01c85c09482b9001bcf21790a6d40494a3a5aaf4f8d5bd2884e25499a54a65</t>
+          <t>0xf172f33c4c2b23605bea3d982f0b82c718d3cccf29fa086a1fbcefb977260877</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2254,12 +2278,12 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12.025</t>
+          <t>55.54</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2320,7 +2344,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785458515</t>
+          <t>1785458765</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2330,7 +2354,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>24.416244</t>
+          <t>113.058524</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2347,7 +2371,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x5ecc4ae58c7b78276b0defbe103a322d68a770b3df079f300e5c69c2b4731021</t>
+          <t>0x770626413b7eb60a07b8e7cb17c67cedae414407b96deb76fd5c4807ea3ab23b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2358,17 +2382,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12.025</t>
+          <t>35.175</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2394,7 +2418,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2424,7 +2448,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785458515</t>
+          <t>1785458648</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2434,7 +2458,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>24.416244</t>
+          <t>71.785714</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2451,23 +2475,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xec7f090351108b7b958a5c4fb3783282609cba12a18c5d155c1f5534aef15888</t>
+          <t>0x420fca3536f3ce2e4be9cfdac1490c3e4a1c8f41c1bd5b62c154f6949a0250d6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1440.5</t>
+          <t>35.175</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2528,7 +2552,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785458317</t>
+          <t>1785458648</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2538,7 +2562,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2932.315522</t>
+          <t>71.785714</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2555,23 +2579,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xd8cf4f50c442be3b22b3347558a79fd346b09cc1ef8e9b148523105c1d6f374a</t>
+          <t>0xdb01c85c09482b9001bcf21790a6d40494a3a5aaf4f8d5bd2884e25499a54a65</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1440.5</t>
+          <t>12.025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2632,7 +2656,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785458316</t>
+          <t>1785458515</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2642,7 +2666,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2932.315522</t>
+          <t>24.416244</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2659,39 +2683,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x6227261e94b21a2814a481af754aa21193c650ab023cebd08d07fdd92c227638</t>
+          <t>0x5ecc4ae58c7b78276b0defbe103a322d68a770b3df079f300e5c69c2b4731021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>56.97</t>
+          <t>12.025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.2725</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -2714,7 +2730,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2744,7 +2760,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785457967</t>
+          <t>1785458515</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2754,7 +2770,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>209.06422</t>
+          <t>24.416244</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2771,28 +2787,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xe210f9e86e0bb9e0dd548ab19bdfc825697ddbd94a1f44c6b09e392508136305</t>
+          <t>0xec7f090351108b7b958a5c4fb3783282609cba12a18c5d155c1f5534aef15888</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>33.88744</t>
+          <t>1440.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.7075</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2818,7 +2834,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2848,7 +2864,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785457812</t>
+          <t>1785458317</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2858,7 +2874,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>47.897442</t>
+          <t>2932.315522</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2875,23 +2891,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x357158ee54a7261c9a3de5193f26c50059ecf3942905b81e23da928f3597b963</t>
+          <t>0xd8cf4f50c442be3b22b3347558a79fd346b09cc1ef8e9b148523105c1d6f374a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>310.405</t>
+          <t>1440.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2952,7 +2968,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785457812</t>
+          <t>1785458316</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2962,7 +2978,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>627.080808</t>
+          <t>2932.315522</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2979,31 +2995,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x07d4c22db9e039aaab83659c51b2c610ff2420310c4aa2f6fa5ee9aaa5df5738</t>
+          <t>0x6227261e94b21a2814a481af754aa21193c650ab023cebd08d07fdd92c227638</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>310.405</t>
+          <t>56.97</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.2725</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -3026,7 +3050,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3056,7 +3080,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785457812</t>
+          <t>1785457967</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3066,7 +3090,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>627.080808</t>
+          <t>209.06422</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3083,28 +3107,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x965925cb75ca17bc44d1270de6e7856136b50e2ba8df869b8ba43a9edfa8cd2c</t>
+          <t>0xe210f9e86e0bb9e0dd548ab19bdfc825697ddbd94a1f44c6b09e392508136305</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>111.49999</t>
+          <t>33.88744</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.7075</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3130,7 +3154,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3160,7 +3184,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785457798</t>
+          <t>1785457812</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3170,7 +3194,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>229.896887</t>
+          <t>47.897442</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3187,23 +3211,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x11cdcc8f35a6869fb42fc42979f00e55e1793e1eaf537612d53ad40413422d94</t>
+          <t>0x357158ee54a7261c9a3de5193f26c50059ecf3942905b81e23da928f3597b963</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>111.49999</t>
+          <t>310.405</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3264,7 +3288,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785457797</t>
+          <t>1785457812</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3274,7 +3298,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>229.896887</t>
+          <t>627.080808</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3291,23 +3315,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xb08a5fa81a7996a995791b3f412a72d7c00869095f73062c91c21ec7d19936a7</t>
+          <t>0x07d4c22db9e039aaab83659c51b2c610ff2420310c4aa2f6fa5ee9aaa5df5738</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>310.405</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3368,7 +3392,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785457480</t>
+          <t>1785457812</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3378,7 +3402,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>459.793814</t>
+          <t>627.080808</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3395,18 +3419,18 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xcd0842e0ce38af317ba18078937aa447779373f330d888eda16082ee857c491b</t>
+          <t>0x965925cb75ca17bc44d1270de6e7856136b50e2ba8df869b8ba43a9edfa8cd2c</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>111.49999</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3416,7 +3440,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3442,7 +3466,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3472,7 +3496,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785457479</t>
+          <t>1785457798</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3482,7 +3506,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>459.793814</t>
+          <t>229.896887</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3499,18 +3523,18 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x298fa2b8022c9fc657efcae03bbf1c76286c06ada5e405c0b8c01f690927ea9d</t>
+          <t>0x11cdcc8f35a6869fb42fc42979f00e55e1793e1eaf537612d53ad40413422d94</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>280.25</t>
+          <t>111.49999</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3520,7 +3544,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3546,7 +3570,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3576,7 +3600,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785457343</t>
+          <t>1785457797</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3586,7 +3610,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>577.835052</t>
+          <t>229.896887</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3603,18 +3627,18 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x849609d6471964d5175246b6bc924306468693f7d1aec2da18390bda2d54e0ad</t>
+          <t>0xb08a5fa81a7996a995791b3f412a72d7c00869095f73062c91c21ec7d19936a7</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>280.25</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3624,7 +3648,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3650,7 +3674,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3680,7 +3704,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785457342</t>
+          <t>1785457480</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3690,7 +3714,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>577.835052</t>
+          <t>459.793814</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3707,18 +3731,18 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xbb37e766b7f859769dd38edd2c0b7223eed00c663e6d49a7bfab098f486c206b</t>
+          <t>0xcd0842e0ce38af317ba18078937aa447779373f330d888eda16082ee857c491b</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3784,7 +3808,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785457307</t>
+          <t>1785457479</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3794,7 +3818,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>309.278351</t>
+          <t>459.793814</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3811,18 +3835,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x8f0dbefc5a409af568cf2a038c3e5e0195adaae1692daaf1ec7d82108ff43db8</t>
+          <t>0x298fa2b8022c9fc657efcae03bbf1c76286c06ada5e405c0b8c01f690927ea9d</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>280.25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3888,7 +3912,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785457307</t>
+          <t>1785457343</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3898,7 +3922,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>309.278351</t>
+          <t>577.835052</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3915,28 +3939,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x9b20bc474ab348aac134c9be069f670928a6c80a3155e27f3467f12716165c53</t>
+          <t>0x849609d6471964d5175246b6bc924306468693f7d1aec2da18390bda2d54e0ad</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>280.25</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3962,7 +3986,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3992,7 +4016,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785457201</t>
+          <t>1785457342</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4002,7 +4026,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>510.769231</t>
+          <t>577.835052</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4019,23 +4043,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x3dda88350d6105418404aee1ac185f1858e87b0aba5134695793d721acf1d81d</t>
+          <t>0xbb37e766b7f859769dd38edd2c0b7223eed00c663e6d49a7bfab098f486c206b</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4096,7 +4120,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785457201</t>
+          <t>1785457307</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4106,7 +4130,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>510.769231</t>
+          <t>309.278351</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4123,7 +4147,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xee9612e6509257c9ad940ec42c374586652e12c5853e386c48508431fbe76d05</t>
+          <t>0x8f0dbefc5a409af568cf2a038c3e5e0195adaae1692daaf1ec7d82108ff43db8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4139,7 +4163,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4200,7 +4224,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785456804</t>
+          <t>1785457307</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4210,7 +4234,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>307.692308</t>
+          <t>309.278351</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4227,18 +4251,18 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x6ba83cbce2c597c47ad2be6ba26f984375bb5e0a7536df8e0c8b906cdd3cf4b5</t>
+          <t>0x9b20bc474ab348aac134c9be069f670928a6c80a3155e27f3467f12716165c53</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4248,7 +4272,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4274,7 +4298,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4304,7 +4328,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785456804</t>
+          <t>1785457201</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4314,7 +4338,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>307.692308</t>
+          <t>510.769231</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4331,28 +4355,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x8fd96b8c3d361ca4f5d4c858af827e49ded210592392fcd9b074b2a925deaca5</t>
+          <t>0x3dda88350d6105418404aee1ac185f1858e87b0aba5134695793d721acf1d81d</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -4378,7 +4402,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4408,7 +4432,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785456147</t>
+          <t>1785457201</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4418,7 +4442,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>58.890756</t>
+          <t>510.769231</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4435,28 +4459,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x0d8a3334c7809cd2635630f68c141dd8605f414e3fbfb296be4eac2929105fda</t>
+          <t>0xee9612e6509257c9ad940ec42c374586652e12c5853e386c48508431fbe76d05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4482,7 +4506,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4512,7 +4536,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785456119</t>
+          <t>1785456804</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4522,7 +4546,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>58.890756</t>
+          <t>307.692308</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4539,28 +4563,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xda8af1defc8a29c16e0370161d4a270c766a68fd83aaaeabab9e4378a0673c8d</t>
+          <t>0x6ba83cbce2c597c47ad2be6ba26f984375bb5e0a7536df8e0c8b906cdd3cf4b5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>14.76</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4586,7 +4610,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4616,7 +4640,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785456113</t>
+          <t>1785456804</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4626,7 +4650,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>307.692308</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4643,28 +4667,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x6455a52d539e6161d9660f2b64423ad8c44b72329f3184934b7abf12459e522b</t>
+          <t>0x8fd96b8c3d361ca4f5d4c858af827e49ded210592392fcd9b074b2a925deaca5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4690,7 +4714,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4720,7 +4744,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785456018</t>
+          <t>1785456147</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4730,7 +4754,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>5.333333</t>
+          <t>58.890756</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4747,28 +4771,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xf8952a0d91c993a93b0aa47a324ed3d061daa3d53d2a7d88bb539b259c373f92</t>
+          <t>0x0d8a3334c7809cd2635630f68c141dd8605f414e3fbfb296be4eac2929105fda</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4794,7 +4818,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4824,7 +4848,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785456003</t>
+          <t>1785456119</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4834,7 +4858,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>5.209877</t>
+          <t>58.890756</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4851,7 +4875,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x999afcdc39345ad0d2e993258d3826f21e43481b2950dcb0f638f2992ac4e4f6</t>
+          <t>0xda8af1defc8a29c16e0370161d4a270c766a68fd83aaaeabab9e4378a0673c8d</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4859,31 +4883,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.9244</t>
+          <t>14.76</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -4906,7 +4922,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4936,7 +4952,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785454208</t>
+          <t>1785456113</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4946,7 +4962,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2.88875</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4963,7 +4979,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xf482d08d1fd572eed4c342d8ff10a66ebe3280fdda896e40e465f342e911ccd5</t>
+          <t>0x6455a52d539e6161d9660f2b64423ad8c44b72329f3184934b7abf12459e522b</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4971,31 +4987,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5018,7 +5026,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5048,7 +5056,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785454207</t>
+          <t>1785456018</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5058,7 +5066,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>40.064</t>
+          <t>5.333333</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5075,7 +5083,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xee4006c4eddaff028b23356cb7de9590b5936ce913b2d1805c50154d5126e6e0</t>
+          <t>0xf8952a0d91c993a93b0aa47a324ed3d061daa3d53d2a7d88bb539b259c373f92</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5083,31 +5091,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785454207</t>
+          <t>1785456003</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5.209877</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5187,31 +5187,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x767f70e59b8e41cdfebda1051f2fa906a012de9bfa55942c59f4f2146ac6192f</t>
+          <t>0x999afcdc39345ad0d2e993258d3826f21e43481b2950dcb0f638f2992ac4e4f6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x1ea5530Db70D5dA696cC1038be611Be53Db5C60F</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>0.9244</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5234,7 +5242,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5264,7 +5272,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785440016</t>
+          <t>1785454208</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5274,7 +5282,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>444.239631</t>
+          <t>2.88875</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5291,7 +5299,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x407971887685061312685cb0b7f5ef9ed6261d2f1b2d1f09c45aa4eae0a05e25</t>
+          <t>0xf482d08d1fd572eed4c342d8ff10a66ebe3280fdda896e40e465f342e911ccd5</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5299,23 +5307,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.57999</t>
+          <t>12.52</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5338,7 +5354,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5368,7 +5384,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785434777</t>
+          <t>1785454207</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5378,7 +5394,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>6.59906</t>
+          <t>40.064</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5395,31 +5411,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
+          <t>0xee4006c4eddaff028b23356cb7de9590b5936ce913b2d1805c50154d5126e6e0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>60.05998</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.7575</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5427,27 +5451,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19614187</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5472,17 +5496,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785400533</t>
+          <t>1785454207</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>79.287102</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5499,54 +5523,46 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+          <t>0x767f70e59b8e41cdfebda1051f2fa906a012de9bfa55942c59f4f2146ac6192f</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x1ea5530Db70D5dA696cC1038be611Be53Db5C60F</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.6637</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>Atlético Bucaramanga</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>Llaneros FC</t>
@@ -5554,7 +5570,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5584,7 +5600,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785344668</t>
+          <t>1785440016</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5594,7 +5610,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1.506591</t>
+          <t>444.239631</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5611,110 +5627,430 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>0x407971887685061312685cb0b7f5ef9ed6261d2f1b2d1f09c45aa4eae0a05e25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3.57999</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.5425</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1785434777</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>6.59906</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>60.05998</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.7575</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>CDP Junior FC vs Millonarios</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>CDP Junior FC</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19606649</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1785400533</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1785633300</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>79.287102</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.6637</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1785344668</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1.506591</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>0xb99da8b648376c357d13a6060e6f4dc2ae7491c558b543e4c668392cdfe2e5bd</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>0.99999</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>1.6987</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Primera A</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Deportivo Pereira</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>0xd09cb30bf0c8317660cdcbbfc8ea542253305047aabd0fa7acee0ff117d36274</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>L19596272</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
         <is>
           <t>1785344544</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>1785546000</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>1.431113</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera A/trades.xlsx
+++ b/data/sxbet/ligas/Primera A/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x4e6d8aa3987bcfa005261070885a48fd586f27d2bc70935198f0e47d5d57bbc1</t>
+          <t>0x83586daa8b624bb395a9793e6eeaf39c5af7ecf92aca70fcc997d0161b164af1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.2725</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Primera A</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Alianza FC Valledupar 0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Alianza FC Valledupar vs Deportes Tolima</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x99fd85073e61e4ff2811a42fd3c5860bb029aa8bb2842c318e468f64896ecc5e</t>
+          <t>0x4ddfc7fb64d3be5c60749a1a51d33f1a0f7a0fdd73b13c70c2475c7c6e5d5e8b</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19596461</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785565485</t>
+          <t>1785602079</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785618300</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>9.321101</t>
+          <t>33.777778</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xa1c75ce4ff8b084ebb89ef9c554b972ba868d695f41f84d5d7eba65ab3bf430e</t>
+          <t>0x84ff211f672e64e5d239f5382404f6df83a2f9b564faf4d9352f9a40a2858896</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19.817</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Primera A</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Alianza FC Valledupar 0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Alianza FC Valledupar vs Deportes Tolima</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x175c82298fd904f82cec6e6df95a6caa5e2925c38ac62b465dc3c16cbe6d7468</t>
+          <t>0x4ddfc7fb64d3be5c60749a1a51d33f1a0f7a0fdd73b13c70c2475c7c6e5d5e8b</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19596461</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785565483</t>
+          <t>1785600148</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785618300</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>20.460358</t>
+          <t>37.657007</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x804741c7cadd40e1de9b46da558e4f8f76822d01b445af10dcb9b394ea6818b4</t>
+          <t>0xac2cdbb4245f52c679b04de9218642f91f9f0d418f7421c33d5b7419c6453ec1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -763,31 +763,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9.99998</t>
+          <t>23.99956</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.7525</t>
+          <t>1.665</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -795,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Alianza FC Valledupar vs Deportes Tolima</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x3461ee17d707212e3a9027bdc8a10f2a6481bbeefaa491f85e9dad2fc6ef04cd</t>
+          <t>0xcf149e7edabae12c7cce191667def8c5527e5a2a4a0b1139d7dbc0ee55cb0657</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19596461</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785565483</t>
+          <t>1785598651</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785618300</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>13.28901</t>
+          <t>36.089564</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x7c7a7beca6e326a985496bfa5683eb5fa550e0b516fd6ce073773eb404203a24</t>
+          <t>0x4e6d8aa3987bcfa005261070885a48fd586f27d2bc70935198f0e47d5d57bbc1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,22 +874,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.2725</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF -1</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -907,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF vs Deportivo Pereira</t>
+          <t>CDP Junior FC vs Millonarios</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>CDP Junior FC</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
+          <t>0x99fd85073e61e4ff2811a42fd3c5860bb029aa8bb2842c318e468f64896ecc5e</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19596272</t>
+          <t>L19606649</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785508565</t>
+          <t>1785565485</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785546000</t>
+          <t>1785633300</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2074.074074</t>
+          <t>9.321101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,12 +971,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xd193b26f2bd560add82739bdab75d53f792eabeb2448f88b702c3e11effb030c</t>
+          <t>0xa1c75ce4ff8b084ebb89ef9c554b972ba868d695f41f84d5d7eba65ab3bf430e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -994,22 +986,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>999.99999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF -1</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1019,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF vs Deportivo Pereira</t>
+          <t>CDP Junior FC vs Millonarios</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>CDP Junior FC</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
+          <t>0x175c82298fd904f82cec6e6df95a6caa5e2925c38ac62b465dc3c16cbe6d7468</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19596272</t>
+          <t>L19606649</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1064,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785508452</t>
+          <t>1785565483</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785546000</t>
+          <t>1785633300</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1980.198</t>
+          <t>20.460358</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,12 +1083,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xdcff50b650be0657ac4bc1268770ca1b1ea0c65c290a0a114d293e00512af266</t>
+          <t>0x804741c7cadd40e1de9b46da558e4f8f76822d01b445af10dcb9b394ea6818b4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1106,22 +1098,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>9.99998</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.7525</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF -1</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1131,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF vs Deportivo Pereira</t>
+          <t>CDP Junior FC vs Millonarios</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>CDP Junior FC</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
+          <t>0x3461ee17d707212e3a9027bdc8a10f2a6481bbeefaa491f85e9dad2fc6ef04cd</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19596272</t>
+          <t>L19606649</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1176,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785508288</t>
+          <t>1785565483</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785546000</t>
+          <t>1785633300</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>597.014925</t>
+          <t>13.28901</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1203,12 +1195,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xa40848b46172c1286780eed941c034eeb3a03a4e6390b868015e86a64c340cbf</t>
+          <t>0x7c7a7beca6e326a985496bfa5683eb5fa550e0b516fd6ce073773eb404203a24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1218,12 +1210,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>906.8</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1288,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785508285</t>
+          <t>1785508565</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1298,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1804.577114</t>
+          <t>2074.074074</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1315,12 +1307,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x74b91529e11bc9b801aabc69fc095fca7f0d47339dbee7f0423c6e1fe35b3c56</t>
+          <t>0xd193b26f2bd560add82739bdab75d53f792eabeb2448f88b702c3e11effb030c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1330,12 +1322,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>999.99999</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1400,7 +1392,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785508244</t>
+          <t>1785508452</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1410,7 +1402,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>597.014925</t>
+          <t>1980.198</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1427,12 +1419,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xedba5ec6631e3639ff5145bb305ece20e8b3069364c2fe3934ad13a18e2004f2</t>
+          <t>0xdcff50b650be0657ac4bc1268770ca1b1ea0c65c290a0a114d293e00512af266</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1442,22 +1434,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.2725</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Fortaleza CEIF -1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1467,27 +1459,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1512,17 +1504,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785459663</t>
+          <t>1785508288</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>68.697248</t>
+          <t>597.014925</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1539,31 +1531,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xa9091dfd45d7760564c0997da3a60bab168f54643ab31141aca0ab8e9ec81033</t>
+          <t>0xa40848b46172c1286780eed941c034eeb3a03a4e6390b868015e86a64c340cbf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>141.53</t>
+          <t>906.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF -1</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -1571,27 +1571,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1616,17 +1616,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785459106</t>
+          <t>1785508285</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>288.101781</t>
+          <t>1804.577114</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1643,23 +1643,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x70dfc6080b5ce53089fea0fe9e58e8db2d467e73911ac1c24f0e3132eeff93ff</t>
+          <t>0x74b91529e11bc9b801aabc69fc095fca7f0d47339dbee7f0423c6e1fe35b3c56</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>141.53</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1667,7 +1671,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF -1</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -1675,27 +1683,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1720,17 +1728,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785459106</t>
+          <t>1785508244</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>288.101781</t>
+          <t>597.014925</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1747,31 +1755,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xda5a2ca0728ab585a3a0a417b6b9bc3201516e60647947d6c517fe5aa3b61048</t>
+          <t>0xedba5ec6631e3639ff5145bb305ece20e8b3069364c2fe3934ad13a18e2004f2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6.485</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.2725</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -1794,7 +1810,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1824,7 +1840,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785459011</t>
+          <t>1785459663</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1834,7 +1850,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>13.167513</t>
+          <t>68.697248</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1851,23 +1867,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x0331bf2d5e4c5647823514fbecd4538f8b83f08eca73864d773e7766b093fb2a</t>
+          <t>0xa9091dfd45d7760564c0997da3a60bab168f54643ab31141aca0ab8e9ec81033</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6.485</t>
+          <t>141.53</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1928,7 +1944,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785459011</t>
+          <t>1785459106</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1938,7 +1954,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>13.167513</t>
+          <t>288.101781</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,18 +1971,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x7c7ef31eaf86810e695207fb33fbd17c8a9667464f034b54067116201439a051</t>
+          <t>0x70dfc6080b5ce53089fea0fe9e58e8db2d467e73911ac1c24f0e3132eeff93ff</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>141.53</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1976,7 +1992,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -2002,7 +2018,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2032,7 +2048,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785458828</t>
+          <t>1785459106</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2042,7 +2058,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>13.964377</t>
+          <t>288.101781</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,7 +2075,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x4bae0ce9888d9df37c25c3bd52c2cef2988011ef9500547215ff3c01a8d9ade3</t>
+          <t>0xda5a2ca0728ab585a3a0a417b6b9bc3201516e60647947d6c517fe5aa3b61048</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2070,12 +2086,12 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>6.485</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2136,7 +2152,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785458828</t>
+          <t>1785459011</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2146,7 +2162,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>13.964377</t>
+          <t>13.167513</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2163,7 +2179,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xf11827477b399686fb93d667a743105e76379dbd2b6ac26fe365b2efa2755088</t>
+          <t>0x0331bf2d5e4c5647823514fbecd4538f8b83f08eca73864d773e7766b093fb2a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2174,17 +2190,17 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>55.54</t>
+          <t>6.485</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2210,7 +2226,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2240,7 +2256,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785458766</t>
+          <t>1785459011</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2250,7 +2266,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>113.058524</t>
+          <t>13.167513</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2267,7 +2283,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xf172f33c4c2b23605bea3d982f0b82c718d3cccf29fa086a1fbcefb977260877</t>
+          <t>0x7c7ef31eaf86810e695207fb33fbd17c8a9667464f034b54067116201439a051</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2278,7 +2294,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>55.54</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2344,7 +2360,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785458765</t>
+          <t>1785458828</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2354,7 +2370,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>113.058524</t>
+          <t>13.964377</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,7 +2387,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x770626413b7eb60a07b8e7cb17c67cedae414407b96deb76fd5c4807ea3ab23b</t>
+          <t>0x4bae0ce9888d9df37c25c3bd52c2cef2988011ef9500547215ff3c01a8d9ade3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2382,17 +2398,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>35.175</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2418,7 +2434,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2448,7 +2464,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785458648</t>
+          <t>1785458828</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2458,7 +2474,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>71.785714</t>
+          <t>13.964377</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,7 +2491,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x420fca3536f3ce2e4be9cfdac1490c3e4a1c8f41c1bd5b62c154f6949a0250d6</t>
+          <t>0xf11827477b399686fb93d667a743105e76379dbd2b6ac26fe365b2efa2755088</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2486,12 +2502,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>35.175</t>
+          <t>55.54</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2552,7 +2568,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785458648</t>
+          <t>1785458766</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2562,7 +2578,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>71.785714</t>
+          <t>113.058524</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2579,7 +2595,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xdb01c85c09482b9001bcf21790a6d40494a3a5aaf4f8d5bd2884e25499a54a65</t>
+          <t>0xf172f33c4c2b23605bea3d982f0b82c718d3cccf29fa086a1fbcefb977260877</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2590,12 +2606,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12.025</t>
+          <t>55.54</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2656,7 +2672,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785458515</t>
+          <t>1785458765</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2666,7 +2682,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>24.416244</t>
+          <t>113.058524</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,7 +2699,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x5ecc4ae58c7b78276b0defbe103a322d68a770b3df079f300e5c69c2b4731021</t>
+          <t>0x770626413b7eb60a07b8e7cb17c67cedae414407b96deb76fd5c4807ea3ab23b</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2694,17 +2710,17 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>12.025</t>
+          <t>35.175</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2730,7 +2746,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2760,7 +2776,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785458515</t>
+          <t>1785458648</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2770,7 +2786,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>24.416244</t>
+          <t>71.785714</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,23 +2803,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xec7f090351108b7b958a5c4fb3783282609cba12a18c5d155c1f5534aef15888</t>
+          <t>0x420fca3536f3ce2e4be9cfdac1490c3e4a1c8f41c1bd5b62c154f6949a0250d6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1440.5</t>
+          <t>35.175</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2864,7 +2880,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785458317</t>
+          <t>1785458648</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2874,7 +2890,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2932.315522</t>
+          <t>71.785714</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2891,23 +2907,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xd8cf4f50c442be3b22b3347558a79fd346b09cc1ef8e9b148523105c1d6f374a</t>
+          <t>0xdb01c85c09482b9001bcf21790a6d40494a3a5aaf4f8d5bd2884e25499a54a65</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1440.5</t>
+          <t>12.025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2968,7 +2984,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785458316</t>
+          <t>1785458515</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2978,7 +2994,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2932.315522</t>
+          <t>24.416244</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2995,39 +3011,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x6227261e94b21a2814a481af754aa21193c650ab023cebd08d07fdd92c227638</t>
+          <t>0x5ecc4ae58c7b78276b0defbe103a322d68a770b3df079f300e5c69c2b4731021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>56.97</t>
+          <t>12.025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.2725</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -3050,7 +3058,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3080,7 +3088,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785457967</t>
+          <t>1785458515</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3090,7 +3098,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>209.06422</t>
+          <t>24.416244</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,28 +3115,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xe210f9e86e0bb9e0dd548ab19bdfc825697ddbd94a1f44c6b09e392508136305</t>
+          <t>0xec7f090351108b7b958a5c4fb3783282609cba12a18c5d155c1f5534aef15888</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>33.88744</t>
+          <t>1440.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.7075</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3154,7 +3162,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3184,7 +3192,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785457812</t>
+          <t>1785458317</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3194,7 +3202,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>47.897442</t>
+          <t>2932.315522</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3211,23 +3219,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x357158ee54a7261c9a3de5193f26c50059ecf3942905b81e23da928f3597b963</t>
+          <t>0xd8cf4f50c442be3b22b3347558a79fd346b09cc1ef8e9b148523105c1d6f374a</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>310.405</t>
+          <t>1440.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3288,7 +3296,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785457812</t>
+          <t>1785458316</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3298,7 +3306,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>627.080808</t>
+          <t>2932.315522</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3315,31 +3323,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x07d4c22db9e039aaab83659c51b2c610ff2420310c4aa2f6fa5ee9aaa5df5738</t>
+          <t>0x6227261e94b21a2814a481af754aa21193c650ab023cebd08d07fdd92c227638</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>310.405</t>
+          <t>56.97</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.2725</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -3362,7 +3378,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3392,7 +3408,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785457812</t>
+          <t>1785457967</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3402,7 +3418,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>627.080808</t>
+          <t>209.06422</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3419,28 +3435,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x965925cb75ca17bc44d1270de6e7856136b50e2ba8df869b8ba43a9edfa8cd2c</t>
+          <t>0xe210f9e86e0bb9e0dd548ab19bdfc825697ddbd94a1f44c6b09e392508136305</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>111.49999</t>
+          <t>33.88744</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.7075</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3466,7 +3482,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3496,7 +3512,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785457798</t>
+          <t>1785457812</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3506,7 +3522,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>229.896887</t>
+          <t>47.897442</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3523,23 +3539,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x11cdcc8f35a6869fb42fc42979f00e55e1793e1eaf537612d53ad40413422d94</t>
+          <t>0x357158ee54a7261c9a3de5193f26c50059ecf3942905b81e23da928f3597b963</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>111.49999</t>
+          <t>310.405</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3600,7 +3616,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785457797</t>
+          <t>1785457812</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3610,7 +3626,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>229.896887</t>
+          <t>627.080808</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3627,23 +3643,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xb08a5fa81a7996a995791b3f412a72d7c00869095f73062c91c21ec7d19936a7</t>
+          <t>0x07d4c22db9e039aaab83659c51b2c610ff2420310c4aa2f6fa5ee9aaa5df5738</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>310.405</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3704,7 +3720,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785457480</t>
+          <t>1785457812</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3714,7 +3730,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>459.793814</t>
+          <t>627.080808</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3731,18 +3747,18 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xcd0842e0ce38af317ba18078937aa447779373f330d888eda16082ee857c491b</t>
+          <t>0x965925cb75ca17bc44d1270de6e7856136b50e2ba8df869b8ba43a9edfa8cd2c</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>111.49999</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3752,7 +3768,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3778,7 +3794,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3808,7 +3824,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785457479</t>
+          <t>1785457798</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3818,7 +3834,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>459.793814</t>
+          <t>229.896887</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3835,18 +3851,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x298fa2b8022c9fc657efcae03bbf1c76286c06ada5e405c0b8c01f690927ea9d</t>
+          <t>0x11cdcc8f35a6869fb42fc42979f00e55e1793e1eaf537612d53ad40413422d94</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>280.25</t>
+          <t>111.49999</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3856,7 +3872,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3882,7 +3898,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3912,7 +3928,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785457343</t>
+          <t>1785457797</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3922,7 +3938,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>577.835052</t>
+          <t>229.896887</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3939,18 +3955,18 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x849609d6471964d5175246b6bc924306468693f7d1aec2da18390bda2d54e0ad</t>
+          <t>0xb08a5fa81a7996a995791b3f412a72d7c00869095f73062c91c21ec7d19936a7</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>280.25</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3960,7 +3976,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3986,7 +4002,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4016,7 +4032,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785457342</t>
+          <t>1785457480</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4026,7 +4042,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>577.835052</t>
+          <t>459.793814</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4043,18 +4059,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xbb37e766b7f859769dd38edd2c0b7223eed00c663e6d49a7bfab098f486c206b</t>
+          <t>0xcd0842e0ce38af317ba18078937aa447779373f330d888eda16082ee857c491b</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4120,7 +4136,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785457307</t>
+          <t>1785457479</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4130,7 +4146,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>309.278351</t>
+          <t>459.793814</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4147,18 +4163,18 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x8f0dbefc5a409af568cf2a038c3e5e0195adaae1692daaf1ec7d82108ff43db8</t>
+          <t>0x298fa2b8022c9fc657efcae03bbf1c76286c06ada5e405c0b8c01f690927ea9d</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>280.25</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4224,7 +4240,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785457307</t>
+          <t>1785457343</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4234,7 +4250,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>309.278351</t>
+          <t>577.835052</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4251,28 +4267,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x9b20bc474ab348aac134c9be069f670928a6c80a3155e27f3467f12716165c53</t>
+          <t>0x849609d6471964d5175246b6bc924306468693f7d1aec2da18390bda2d54e0ad</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>280.25</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4298,7 +4314,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4328,7 +4344,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785457201</t>
+          <t>1785457342</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4338,7 +4354,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>510.769231</t>
+          <t>577.835052</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4355,23 +4371,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x3dda88350d6105418404aee1ac185f1858e87b0aba5134695793d721acf1d81d</t>
+          <t>0xbb37e766b7f859769dd38edd2c0b7223eed00c663e6d49a7bfab098f486c206b</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4432,7 +4448,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785457201</t>
+          <t>1785457307</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4442,7 +4458,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>510.769231</t>
+          <t>309.278351</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4459,7 +4475,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xee9612e6509257c9ad940ec42c374586652e12c5853e386c48508431fbe76d05</t>
+          <t>0x8f0dbefc5a409af568cf2a038c3e5e0195adaae1692daaf1ec7d82108ff43db8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4475,7 +4491,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4536,7 +4552,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785456804</t>
+          <t>1785457307</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4546,7 +4562,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>307.692308</t>
+          <t>309.278351</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4563,18 +4579,18 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x6ba83cbce2c597c47ad2be6ba26f984375bb5e0a7536df8e0c8b906cdd3cf4b5</t>
+          <t>0x9b20bc474ab348aac134c9be069f670928a6c80a3155e27f3467f12716165c53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4584,7 +4600,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4610,7 +4626,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4640,7 +4656,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785456804</t>
+          <t>1785457201</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4650,7 +4666,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>307.692308</t>
+          <t>510.769231</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4667,28 +4683,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x8fd96b8c3d361ca4f5d4c858af827e49ded210592392fcd9b074b2a925deaca5</t>
+          <t>0x3dda88350d6105418404aee1ac185f1858e87b0aba5134695793d721acf1d81d</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4714,7 +4730,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4744,7 +4760,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785456147</t>
+          <t>1785457201</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4754,7 +4770,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>58.890756</t>
+          <t>510.769231</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4771,28 +4787,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x0d8a3334c7809cd2635630f68c141dd8605f414e3fbfb296be4eac2929105fda</t>
+          <t>0xee9612e6509257c9ad940ec42c374586652e12c5853e386c48508431fbe76d05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4818,7 +4834,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4848,7 +4864,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785456119</t>
+          <t>1785456804</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4858,7 +4874,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>58.890756</t>
+          <t>307.692308</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4875,28 +4891,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xda8af1defc8a29c16e0370161d4a270c766a68fd83aaaeabab9e4378a0673c8d</t>
+          <t>0x6ba83cbce2c597c47ad2be6ba26f984375bb5e0a7536df8e0c8b906cdd3cf4b5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>14.76</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4922,7 +4938,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4952,7 +4968,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785456113</t>
+          <t>1785456804</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4962,7 +4978,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>307.692308</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4979,28 +4995,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x6455a52d539e6161d9660f2b64423ad8c44b72329f3184934b7abf12459e522b</t>
+          <t>0x8fd96b8c3d361ca4f5d4c858af827e49ded210592392fcd9b074b2a925deaca5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5026,7 +5042,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5056,7 +5072,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785456018</t>
+          <t>1785456147</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5066,7 +5082,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>5.333333</t>
+          <t>58.890756</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5083,28 +5099,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xf8952a0d91c993a93b0aa47a324ed3d061daa3d53d2a7d88bb539b259c373f92</t>
+          <t>0x0d8a3334c7809cd2635630f68c141dd8605f414e3fbfb296be4eac2929105fda</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5130,7 +5146,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5160,7 +5176,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785456003</t>
+          <t>1785456119</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5170,7 +5186,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>5.209877</t>
+          <t>58.890756</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5187,7 +5203,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x999afcdc39345ad0d2e993258d3826f21e43481b2950dcb0f638f2992ac4e4f6</t>
+          <t>0xda8af1defc8a29c16e0370161d4a270c766a68fd83aaaeabab9e4378a0673c8d</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5195,31 +5211,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.9244</t>
+          <t>14.76</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5242,7 +5250,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5272,7 +5280,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785454208</t>
+          <t>1785456113</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5282,7 +5290,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2.88875</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5299,7 +5307,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xf482d08d1fd572eed4c342d8ff10a66ebe3280fdda896e40e465f342e911ccd5</t>
+          <t>0x6455a52d539e6161d9660f2b64423ad8c44b72329f3184934b7abf12459e522b</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5307,31 +5315,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785454207</t>
+          <t>1785456018</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>40.064</t>
+          <t>5.333333</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5411,7 +5411,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xee4006c4eddaff028b23356cb7de9590b5936ce913b2d1805c50154d5126e6e0</t>
+          <t>0xf8952a0d91c993a93b0aa47a324ed3d061daa3d53d2a7d88bb539b259c373f92</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5419,31 +5419,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5466,7 +5458,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5496,7 +5488,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785454207</t>
+          <t>1785456003</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5506,7 +5498,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5.209877</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5523,31 +5515,39 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x767f70e59b8e41cdfebda1051f2fa906a012de9bfa55942c59f4f2146ac6192f</t>
+          <t>0x999afcdc39345ad0d2e993258d3826f21e43481b2950dcb0f638f2992ac4e4f6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x1ea5530Db70D5dA696cC1038be611Be53Db5C60F</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>0.9244</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785440016</t>
+          <t>1785454208</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>444.239631</t>
+          <t>2.88875</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5627,7 +5627,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x407971887685061312685cb0b7f5ef9ed6261d2f1b2d1f09c45aa4eae0a05e25</t>
+          <t>0xf482d08d1fd572eed4c342d8ff10a66ebe3280fdda896e40e465f342e911ccd5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5635,23 +5635,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3.57999</t>
+          <t>12.52</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5674,7 +5682,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5704,7 +5712,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785434777</t>
+          <t>1785454207</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5714,7 +5722,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>6.59906</t>
+          <t>40.064</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5731,31 +5739,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
+          <t>0xee4006c4eddaff028b23356cb7de9590b5936ce913b2d1805c50154d5126e6e0</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>60.05998</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.7575</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5763,27 +5779,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19614187</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5808,17 +5824,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785400533</t>
+          <t>1785454207</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>79.287102</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5835,54 +5851,46 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+          <t>0x767f70e59b8e41cdfebda1051f2fa906a012de9bfa55942c59f4f2146ac6192f</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x1ea5530Db70D5dA696cC1038be611Be53Db5C60F</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.6637</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>Atlético Bucaramanga</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>Llaneros FC</t>
@@ -5890,7 +5898,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5920,7 +5928,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785344668</t>
+          <t>1785440016</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5930,7 +5938,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1.506591</t>
+          <t>444.239631</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5947,110 +5955,430 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>0x407971887685061312685cb0b7f5ef9ed6261d2f1b2d1f09c45aa4eae0a05e25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3.57999</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.5425</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1785434777</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>6.59906</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>60.05998</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.7575</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>CDP Junior FC vs Millonarios</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>CDP Junior FC</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19606649</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1785400533</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1785633300</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>79.287102</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.6637</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1785344668</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1.506591</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>0xb99da8b648376c357d13a6060e6f4dc2ae7491c558b543e4c668392cdfe2e5bd</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>0.99999</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>1.6987</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Primera A</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>Deportivo Pereira</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>0xd09cb30bf0c8317660cdcbbfc8ea542253305047aabd0fa7acee0ff117d36274</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>L19596272</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
         <is>
           <t>1785344544</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>1785546000</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>1.431113</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera A/trades.xlsx
+++ b/data/sxbet/ligas/Primera A/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:V58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x83586daa8b624bb395a9793e6eeaf39c5af7ecf92aca70fcc997d0161b164af1</t>
+          <t>0xe6bce4fd7847619685cae46bf904c43059efb54cbabb07837cd276c69a9cac8c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,52 +546,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>Primera A</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Alianza FC Valledupar 0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar vs Deportes Tolima</t>
+          <t>Deportivo Pasto vs Rionegro Aguilas</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Deportes Tolima</t>
+          <t>Rionegro Aguilas</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x4ddfc7fb64d3be5c60749a1a51d33f1a0f7a0fdd73b13c70c2475c7c6e5d5e8b</t>
+          <t>0x087d60f2b64530b4e99ae6c48561d5b3386ce094838052c4e0fec7c1f1178667</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19596461</t>
+          <t>L19596456</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785602079</t>
+          <t>1785604435</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785618300</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>33.777778</t>
+          <t>9.070295</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x84ff211f672e64e5d239f5382404f6df83a2f9b564faf4d9352f9a40a2858896</t>
+          <t>0x3b6dd2c698f7aff2bed5984985fcb070deff0a89975871642ce3dcfc7d1f75f6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,52 +658,52 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19.817</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>Primera A</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Alianza FC Valledupar 0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar vs Deportes Tolima</t>
+          <t>Deportivo Pasto vs Rionegro Aguilas</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Deportes Tolima</t>
+          <t>Rionegro Aguilas</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x4ddfc7fb64d3be5c60749a1a51d33f1a0f7a0fdd73b13c70c2475c7c6e5d5e8b</t>
+          <t>0x087d60f2b64530b4e99ae6c48561d5b3386ce094838052c4e0fec7c1f1178667</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19596461</t>
+          <t>L19596456</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785600148</t>
+          <t>1785604420</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785618300</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>37.657007</t>
+          <t>25.052154</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xac2cdbb4245f52c679b04de9218642f91f9f0d418f7421c33d5b7419c6453ec1</t>
+          <t>0x83586daa8b624bb395a9793e6eeaf39c5af7ecf92aca70fcc997d0161b164af1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -763,23 +763,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23.99956</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.665</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alianza FC Valledupar 0</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -802,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xcf149e7edabae12c7cce191667def8c5527e5a2a4a0b1139d7dbc0ee55cb0657</t>
+          <t>0x4ddfc7fb64d3be5c60749a1a51d33f1a0f7a0fdd73b13c70c2475c7c6e5d5e8b</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785598651</t>
+          <t>1785602079</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>36.089564</t>
+          <t>33.777778</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x4e6d8aa3987bcfa005261070885a48fd586f27d2bc70935198f0e47d5d57bbc1</t>
+          <t>0x84ff211f672e64e5d239f5382404f6df83a2f9b564faf4d9352f9a40a2858896</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -874,22 +882,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>19.817</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.2725</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Primera A</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Alianza FC Valledupar 0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,27 +907,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Alianza FC Valledupar vs Deportes Tolima</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x99fd85073e61e4ff2811a42fd3c5860bb029aa8bb2842c318e468f64896ecc5e</t>
+          <t>0x4ddfc7fb64d3be5c60749a1a51d33f1a0f7a0fdd73b13c70c2475c7c6e5d5e8b</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19596461</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785565485</t>
+          <t>1785600148</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785618300</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>9.321101</t>
+          <t>37.657007</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xa1c75ce4ff8b084ebb89ef9c554b972ba868d695f41f84d5d7eba65ab3bf430e</t>
+          <t>0xac2cdbb4245f52c679b04de9218642f91f9f0d418f7421c33d5b7419c6453ec1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -979,31 +987,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23.99956</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.665</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -1011,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Alianza FC Valledupar vs Deportes Tolima</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x175c82298fd904f82cec6e6df95a6caa5e2925c38ac62b465dc3c16cbe6d7468</t>
+          <t>0xcf149e7edabae12c7cce191667def8c5527e5a2a4a0b1139d7dbc0ee55cb0657</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19596461</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785565483</t>
+          <t>1785598651</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785618300</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>20.460358</t>
+          <t>36.089564</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x804741c7cadd40e1de9b46da558e4f8f76822d01b445af10dcb9b394ea6818b4</t>
+          <t>0x4e6d8aa3987bcfa005261070885a48fd586f27d2bc70935198f0e47d5d57bbc1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.99998</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.7525</t>
+          <t>1.2725</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x3461ee17d707212e3a9027bdc8a10f2a6481bbeefaa491f85e9dad2fc6ef04cd</t>
+          <t>0x99fd85073e61e4ff2811a42fd3c5860bb029aa8bb2842c318e468f64896ecc5e</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785565483</t>
+          <t>1785565485</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>13.28901</t>
+          <t>9.321101</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x7c7a7beca6e326a985496bfa5683eb5fa550e0b516fd6ce073773eb404203a24</t>
+          <t>0xa1c75ce4ff8b084ebb89ef9c554b972ba868d695f41f84d5d7eba65ab3bf430e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1210,22 +1210,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF -1</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF vs Deportivo Pereira</t>
+          <t>CDP Junior FC vs Millonarios</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>CDP Junior FC</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
+          <t>0x175c82298fd904f82cec6e6df95a6caa5e2925c38ac62b465dc3c16cbe6d7468</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19596272</t>
+          <t>L19606649</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785508565</t>
+          <t>1785565483</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785546000</t>
+          <t>1785633300</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2074.074074</t>
+          <t>20.460358</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,12 +1307,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xd193b26f2bd560add82739bdab75d53f792eabeb2448f88b702c3e11effb030c</t>
+          <t>0x804741c7cadd40e1de9b46da558e4f8f76822d01b445af10dcb9b394ea6818b4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>999.99999</t>
+          <t>9.99998</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.7525</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF -1</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1347,27 +1347,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF vs Deportivo Pereira</t>
+          <t>CDP Junior FC vs Millonarios</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>CDP Junior FC</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
+          <t>0x3461ee17d707212e3a9027bdc8a10f2a6481bbeefaa491f85e9dad2fc6ef04cd</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19596272</t>
+          <t>L19606649</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785508452</t>
+          <t>1785565483</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785546000</t>
+          <t>1785633300</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1980.198</t>
+          <t>13.28901</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xdcff50b650be0657ac4bc1268770ca1b1ea0c65c290a0a114d293e00512af266</t>
+          <t>0x7c7a7beca6e326a985496bfa5683eb5fa550e0b516fd6ce073773eb404203a24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785508288</t>
+          <t>1785508565</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>597.014925</t>
+          <t>2074.074074</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1531,12 +1531,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xa40848b46172c1286780eed941c034eeb3a03a4e6390b868015e86a64c340cbf</t>
+          <t>0xd193b26f2bd560add82739bdab75d53f792eabeb2448f88b702c3e11effb030c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>906.8</t>
+          <t>999.99999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785508285</t>
+          <t>1785508452</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1804.577114</t>
+          <t>1980.198</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1643,7 +1643,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x74b91529e11bc9b801aabc69fc095fca7f0d47339dbee7f0423c6e1fe35b3c56</t>
+          <t>0xdcff50b650be0657ac4bc1268770ca1b1ea0c65c290a0a114d293e00512af266</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785508244</t>
+          <t>1785508288</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xedba5ec6631e3639ff5145bb305ece20e8b3069364c2fe3934ad13a18e2004f2</t>
+          <t>0xa40848b46172c1286780eed941c034eeb3a03a4e6390b868015e86a64c340cbf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1770,22 +1770,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>906.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.2725</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Fortaleza CEIF -1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1795,27 +1795,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785459663</t>
+          <t>1785508285</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>68.697248</t>
+          <t>1804.577114</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1867,31 +1867,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xa9091dfd45d7760564c0997da3a60bab168f54643ab31141aca0ab8e9ec81033</t>
+          <t>0x74b91529e11bc9b801aabc69fc095fca7f0d47339dbee7f0423c6e1fe35b3c56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>141.53</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF -1</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -1899,27 +1907,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1944,17 +1952,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785459106</t>
+          <t>1785508244</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>288.101781</t>
+          <t>597.014925</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1971,31 +1979,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x70dfc6080b5ce53089fea0fe9e58e8db2d467e73911ac1c24f0e3132eeff93ff</t>
+          <t>0xedba5ec6631e3639ff5145bb305ece20e8b3069364c2fe3934ad13a18e2004f2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>141.53</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.2725</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -2018,7 +2034,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2048,7 +2064,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785459106</t>
+          <t>1785459663</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2058,7 +2074,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>288.101781</t>
+          <t>68.697248</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2075,28 +2091,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xda5a2ca0728ab585a3a0a417b6b9bc3201516e60647947d6c517fe5aa3b61048</t>
+          <t>0xa9091dfd45d7760564c0997da3a60bab168f54643ab31141aca0ab8e9ec81033</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.485</t>
+          <t>141.53</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2122,7 +2138,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2152,7 +2168,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785459011</t>
+          <t>1785459106</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2162,7 +2178,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>13.167513</t>
+          <t>288.101781</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2179,28 +2195,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x0331bf2d5e4c5647823514fbecd4538f8b83f08eca73864d773e7766b093fb2a</t>
+          <t>0x70dfc6080b5ce53089fea0fe9e58e8db2d467e73911ac1c24f0e3132eeff93ff</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6.485</t>
+          <t>141.53</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2226,7 +2242,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2256,7 +2272,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785459011</t>
+          <t>1785459106</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2266,7 +2282,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>13.167513</t>
+          <t>288.101781</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,7 +2299,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x7c7ef31eaf86810e695207fb33fbd17c8a9667464f034b54067116201439a051</t>
+          <t>0xda5a2ca0728ab585a3a0a417b6b9bc3201516e60647947d6c517fe5aa3b61048</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2294,17 +2310,17 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>6.485</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2330,7 +2346,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2360,7 +2376,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785458828</t>
+          <t>1785459011</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2370,7 +2386,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13.964377</t>
+          <t>13.167513</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2387,7 +2403,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x4bae0ce9888d9df37c25c3bd52c2cef2988011ef9500547215ff3c01a8d9ade3</t>
+          <t>0x0331bf2d5e4c5647823514fbecd4538f8b83f08eca73864d773e7766b093fb2a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2398,17 +2414,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>6.485</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2434,7 +2450,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2464,7 +2480,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785458828</t>
+          <t>1785459011</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2474,7 +2490,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>13.964377</t>
+          <t>13.167513</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2491,7 +2507,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xf11827477b399686fb93d667a743105e76379dbd2b6ac26fe365b2efa2755088</t>
+          <t>0x7c7ef31eaf86810e695207fb33fbd17c8a9667464f034b54067116201439a051</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2502,7 +2518,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>55.54</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2512,7 +2528,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2538,7 +2554,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2568,7 +2584,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785458766</t>
+          <t>1785458828</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2578,7 +2594,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>113.058524</t>
+          <t>13.964377</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2595,7 +2611,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xf172f33c4c2b23605bea3d982f0b82c718d3cccf29fa086a1fbcefb977260877</t>
+          <t>0x4bae0ce9888d9df37c25c3bd52c2cef2988011ef9500547215ff3c01a8d9ade3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2606,7 +2622,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>55.54</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2616,7 +2632,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2642,7 +2658,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2672,7 +2688,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785458765</t>
+          <t>1785458828</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2682,7 +2698,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>113.058524</t>
+          <t>13.964377</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2699,7 +2715,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x770626413b7eb60a07b8e7cb17c67cedae414407b96deb76fd5c4807ea3ab23b</t>
+          <t>0xf11827477b399686fb93d667a743105e76379dbd2b6ac26fe365b2efa2755088</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2710,17 +2726,17 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>35.175</t>
+          <t>55.54</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2746,7 +2762,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2776,7 +2792,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785458648</t>
+          <t>1785458766</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2786,7 +2802,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>71.785714</t>
+          <t>113.058524</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2803,7 +2819,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x420fca3536f3ce2e4be9cfdac1490c3e4a1c8f41c1bd5b62c154f6949a0250d6</t>
+          <t>0xf172f33c4c2b23605bea3d982f0b82c718d3cccf29fa086a1fbcefb977260877</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2814,17 +2830,17 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>35.175</t>
+          <t>55.54</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2850,7 +2866,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2880,7 +2896,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785458648</t>
+          <t>1785458765</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2890,7 +2906,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>71.785714</t>
+          <t>113.058524</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2907,7 +2923,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xdb01c85c09482b9001bcf21790a6d40494a3a5aaf4f8d5bd2884e25499a54a65</t>
+          <t>0x770626413b7eb60a07b8e7cb17c67cedae414407b96deb76fd5c4807ea3ab23b</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2918,12 +2934,12 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>12.025</t>
+          <t>35.175</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2984,7 +3000,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785458515</t>
+          <t>1785458648</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2994,7 +3010,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>24.416244</t>
+          <t>71.785714</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3011,7 +3027,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x5ecc4ae58c7b78276b0defbe103a322d68a770b3df079f300e5c69c2b4731021</t>
+          <t>0x420fca3536f3ce2e4be9cfdac1490c3e4a1c8f41c1bd5b62c154f6949a0250d6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3022,12 +3038,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12.025</t>
+          <t>35.175</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3088,7 +3104,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785458515</t>
+          <t>1785458648</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3098,7 +3114,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>24.416244</t>
+          <t>71.785714</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3115,28 +3131,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xec7f090351108b7b958a5c4fb3783282609cba12a18c5d155c1f5534aef15888</t>
+          <t>0xdb01c85c09482b9001bcf21790a6d40494a3a5aaf4f8d5bd2884e25499a54a65</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1440.5</t>
+          <t>12.025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3162,7 +3178,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3192,7 +3208,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785458317</t>
+          <t>1785458515</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3202,7 +3218,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2932.315522</t>
+          <t>24.416244</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3219,28 +3235,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xd8cf4f50c442be3b22b3347558a79fd346b09cc1ef8e9b148523105c1d6f374a</t>
+          <t>0x5ecc4ae58c7b78276b0defbe103a322d68a770b3df079f300e5c69c2b4731021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1440.5</t>
+          <t>12.025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3266,7 +3282,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3296,7 +3312,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785458316</t>
+          <t>1785458515</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3306,7 +3322,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2932.315522</t>
+          <t>24.416244</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3323,39 +3339,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x6227261e94b21a2814a481af754aa21193c650ab023cebd08d07fdd92c227638</t>
+          <t>0xec7f090351108b7b958a5c4fb3783282609cba12a18c5d155c1f5534aef15888</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>56.97</t>
+          <t>1440.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.2725</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -3378,7 +3386,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3408,7 +3416,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785457967</t>
+          <t>1785458317</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3418,7 +3426,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>209.06422</t>
+          <t>2932.315522</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3435,28 +3443,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xe210f9e86e0bb9e0dd548ab19bdfc825697ddbd94a1f44c6b09e392508136305</t>
+          <t>0xd8cf4f50c442be3b22b3347558a79fd346b09cc1ef8e9b148523105c1d6f374a</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>33.88744</t>
+          <t>1440.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.7075</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3482,7 +3490,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3512,7 +3520,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785457812</t>
+          <t>1785458316</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3522,7 +3530,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>47.897442</t>
+          <t>2932.315522</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3539,31 +3547,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x357158ee54a7261c9a3de5193f26c50059ecf3942905b81e23da928f3597b963</t>
+          <t>0x6227261e94b21a2814a481af754aa21193c650ab023cebd08d07fdd92c227638</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>310.405</t>
+          <t>56.97</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.2725</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -3586,7 +3602,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3616,7 +3632,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785457812</t>
+          <t>1785457967</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3626,7 +3642,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>627.080808</t>
+          <t>209.06422</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3643,7 +3659,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x07d4c22db9e039aaab83659c51b2c610ff2420310c4aa2f6fa5ee9aaa5df5738</t>
+          <t>0xe210f9e86e0bb9e0dd548ab19bdfc825697ddbd94a1f44c6b09e392508136305</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,17 +3670,17 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>310.405</t>
+          <t>33.88744</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.7075</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3690,7 +3706,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3730,7 +3746,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>627.080808</t>
+          <t>47.897442</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3747,28 +3763,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x965925cb75ca17bc44d1270de6e7856136b50e2ba8df869b8ba43a9edfa8cd2c</t>
+          <t>0x357158ee54a7261c9a3de5193f26c50059ecf3942905b81e23da928f3597b963</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>111.49999</t>
+          <t>310.405</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3794,7 +3810,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3824,7 +3840,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785457798</t>
+          <t>1785457812</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3834,7 +3850,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>229.896887</t>
+          <t>627.080808</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3851,28 +3867,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x11cdcc8f35a6869fb42fc42979f00e55e1793e1eaf537612d53ad40413422d94</t>
+          <t>0x07d4c22db9e039aaab83659c51b2c610ff2420310c4aa2f6fa5ee9aaa5df5738</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>111.49999</t>
+          <t>310.405</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3898,7 +3914,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3928,7 +3944,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785457797</t>
+          <t>1785457812</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3938,7 +3954,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>229.896887</t>
+          <t>627.080808</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3955,18 +3971,18 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xb08a5fa81a7996a995791b3f412a72d7c00869095f73062c91c21ec7d19936a7</t>
+          <t>0x965925cb75ca17bc44d1270de6e7856136b50e2ba8df869b8ba43a9edfa8cd2c</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>111.49999</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4032,7 +4048,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785457480</t>
+          <t>1785457798</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4042,7 +4058,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>459.793814</t>
+          <t>229.896887</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4059,18 +4075,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xcd0842e0ce38af317ba18078937aa447779373f330d888eda16082ee857c491b</t>
+          <t>0x11cdcc8f35a6869fb42fc42979f00e55e1793e1eaf537612d53ad40413422d94</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>111.49999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4136,7 +4152,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785457479</t>
+          <t>1785457797</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4146,7 +4162,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>459.793814</t>
+          <t>229.896887</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4163,18 +4179,18 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x298fa2b8022c9fc657efcae03bbf1c76286c06ada5e405c0b8c01f690927ea9d</t>
+          <t>0xb08a5fa81a7996a995791b3f412a72d7c00869095f73062c91c21ec7d19936a7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>280.25</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4240,7 +4256,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785457343</t>
+          <t>1785457480</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4250,7 +4266,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>577.835052</t>
+          <t>459.793814</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4267,18 +4283,18 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x849609d6471964d5175246b6bc924306468693f7d1aec2da18390bda2d54e0ad</t>
+          <t>0xcd0842e0ce38af317ba18078937aa447779373f330d888eda16082ee857c491b</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>280.25</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4344,7 +4360,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785457342</t>
+          <t>1785457479</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4354,7 +4370,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>577.835052</t>
+          <t>459.793814</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4371,18 +4387,18 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xbb37e766b7f859769dd38edd2c0b7223eed00c663e6d49a7bfab098f486c206b</t>
+          <t>0x298fa2b8022c9fc657efcae03bbf1c76286c06ada5e405c0b8c01f690927ea9d</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>280.25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4392,7 +4408,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -4418,7 +4434,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4448,7 +4464,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785457307</t>
+          <t>1785457343</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4458,7 +4474,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>309.278351</t>
+          <t>577.835052</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4475,18 +4491,18 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x8f0dbefc5a409af568cf2a038c3e5e0195adaae1692daaf1ec7d82108ff43db8</t>
+          <t>0x849609d6471964d5175246b6bc924306468693f7d1aec2da18390bda2d54e0ad</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>280.25</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4496,7 +4512,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4522,7 +4538,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4552,7 +4568,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785457307</t>
+          <t>1785457342</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4562,7 +4578,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>309.278351</t>
+          <t>577.835052</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4579,28 +4595,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x9b20bc474ab348aac134c9be069f670928a6c80a3155e27f3467f12716165c53</t>
+          <t>0xbb37e766b7f859769dd38edd2c0b7223eed00c663e6d49a7bfab098f486c206b</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4626,7 +4642,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4656,7 +4672,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785457201</t>
+          <t>1785457307</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4666,7 +4682,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>510.769231</t>
+          <t>309.278351</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4683,28 +4699,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x3dda88350d6105418404aee1ac185f1858e87b0aba5134695793d721acf1d81d</t>
+          <t>0x8f0dbefc5a409af568cf2a038c3e5e0195adaae1692daaf1ec7d82108ff43db8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4730,7 +4746,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4760,7 +4776,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785457201</t>
+          <t>1785457307</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4770,7 +4786,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>510.769231</t>
+          <t>309.278351</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4787,18 +4803,18 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xee9612e6509257c9ad940ec42c374586652e12c5853e386c48508431fbe76d05</t>
+          <t>0x9b20bc474ab348aac134c9be069f670928a6c80a3155e27f3467f12716165c53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4864,7 +4880,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785456804</t>
+          <t>1785457201</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4874,7 +4890,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>307.692308</t>
+          <t>510.769231</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4891,18 +4907,18 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x6ba83cbce2c597c47ad2be6ba26f984375bb5e0a7536df8e0c8b906cdd3cf4b5</t>
+          <t>0x3dda88350d6105418404aee1ac185f1858e87b0aba5134695793d721acf1d81d</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4968,7 +4984,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785456804</t>
+          <t>1785457201</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4978,7 +4994,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>307.692308</t>
+          <t>510.769231</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4995,28 +5011,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x8fd96b8c3d361ca4f5d4c858af827e49ded210592392fcd9b074b2a925deaca5</t>
+          <t>0xee9612e6509257c9ad940ec42c374586652e12c5853e386c48508431fbe76d05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5042,7 +5058,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5072,7 +5088,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785456147</t>
+          <t>1785456804</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5082,7 +5098,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>58.890756</t>
+          <t>307.692308</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5099,28 +5115,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x0d8a3334c7809cd2635630f68c141dd8605f414e3fbfb296be4eac2929105fda</t>
+          <t>0x6ba83cbce2c597c47ad2be6ba26f984375bb5e0a7536df8e0c8b906cdd3cf4b5</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5146,7 +5162,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5176,7 +5192,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785456119</t>
+          <t>1785456804</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5186,7 +5202,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>58.890756</t>
+          <t>307.692308</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5203,28 +5219,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xda8af1defc8a29c16e0370161d4a270c766a68fd83aaaeabab9e4378a0673c8d</t>
+          <t>0x8fd96b8c3d361ca4f5d4c858af827e49ded210592392fcd9b074b2a925deaca5</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>14.76</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5250,7 +5266,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5280,7 +5296,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785456113</t>
+          <t>1785456147</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5290,7 +5306,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>58.890756</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5307,28 +5323,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x6455a52d539e6161d9660f2b64423ad8c44b72329f3184934b7abf12459e522b</t>
+          <t>0x0d8a3334c7809cd2635630f68c141dd8605f414e3fbfb296be4eac2929105fda</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5354,7 +5370,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5384,7 +5400,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785456018</t>
+          <t>1785456119</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5394,7 +5410,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>5.333333</t>
+          <t>58.890756</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5411,7 +5427,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xf8952a0d91c993a93b0aa47a324ed3d061daa3d53d2a7d88bb539b259c373f92</t>
+          <t>0xda8af1defc8a29c16e0370161d4a270c766a68fd83aaaeabab9e4378a0673c8d</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5422,12 +5438,12 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>14.76</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5488,7 +5504,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785456003</t>
+          <t>1785456113</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5498,7 +5514,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>5.209877</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5515,7 +5531,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x999afcdc39345ad0d2e993258d3826f21e43481b2950dcb0f638f2992ac4e4f6</t>
+          <t>0x6455a52d539e6161d9660f2b64423ad8c44b72329f3184934b7abf12459e522b</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5523,31 +5539,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.9244</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5570,7 +5578,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5600,7 +5608,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785454208</t>
+          <t>1785456018</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5610,7 +5618,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2.88875</t>
+          <t>5.333333</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5627,7 +5635,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xf482d08d1fd572eed4c342d8ff10a66ebe3280fdda896e40e465f342e911ccd5</t>
+          <t>0xf8952a0d91c993a93b0aa47a324ed3d061daa3d53d2a7d88bb539b259c373f92</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5635,31 +5643,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785454207</t>
+          <t>1785456003</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>40.064</t>
+          <t>5.209877</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5739,7 +5739,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xee4006c4eddaff028b23356cb7de9590b5936ce913b2d1805c50154d5126e6e0</t>
+          <t>0x999afcdc39345ad0d2e993258d3826f21e43481b2950dcb0f638f2992ac4e4f6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.9244</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785454207</t>
+          <t>1785454208</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.88875</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5851,31 +5851,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x767f70e59b8e41cdfebda1051f2fa906a012de9bfa55942c59f4f2146ac6192f</t>
+          <t>0xf482d08d1fd572eed4c342d8ff10a66ebe3280fdda896e40e465f342e911ccd5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x1ea5530Db70D5dA696cC1038be611Be53Db5C60F</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>12.52</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5898,7 +5906,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5928,7 +5936,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785440016</t>
+          <t>1785454207</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5938,7 +5946,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>444.239631</t>
+          <t>40.064</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5955,7 +5963,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x407971887685061312685cb0b7f5ef9ed6261d2f1b2d1f09c45aa4eae0a05e25</t>
+          <t>0xee4006c4eddaff028b23356cb7de9590b5936ce913b2d1805c50154d5126e6e0</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5963,23 +5971,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3.57999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -6002,7 +6018,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6032,7 +6048,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785434777</t>
+          <t>1785454207</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6042,7 +6058,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>6.59906</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6059,28 +6075,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
+          <t>0x767f70e59b8e41cdfebda1051f2fa906a012de9bfa55942c59f4f2146ac6192f</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x1ea5530Db70D5dA696cC1038be611Be53Db5C60F</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>60.05998</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.7575</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -6091,27 +6107,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19614187</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6136,17 +6152,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785400533</t>
+          <t>1785440016</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>79.287102</t>
+          <t>444.239631</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6163,54 +6179,46 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+          <t>0x407971887685061312685cb0b7f5ef9ed6261d2f1b2d1f09c45aa4eae0a05e25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3.57999</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.6637</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>Atlético Bucaramanga</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>Llaneros FC</t>
@@ -6218,7 +6226,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6248,7 +6256,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785344668</t>
+          <t>1785434777</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6258,7 +6266,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1.506591</t>
+          <t>6.59906</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6275,110 +6283,326 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>60.05998</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.7575</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>CDP Junior FC vs Millonarios</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>CDP Junior FC</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19606649</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1785400533</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1785633300</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>79.287102</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.6637</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1785344668</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1.506591</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>0xb99da8b648376c357d13a6060e6f4dc2ae7491c558b543e4c668392cdfe2e5bd</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>0.99999</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>1.6987</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Primera A</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>Deportivo Pereira</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>0xd09cb30bf0c8317660cdcbbfc8ea542253305047aabd0fa7acee0ff117d36274</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>L19596272</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
         <is>
           <t>1785344544</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>1785546000</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>1.431113</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Primera A/trades.xlsx
+++ b/data/sxbet/ligas/Primera A/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V58"/>
+  <dimension ref="A1:V61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xe6bce4fd7847619685cae46bf904c43059efb54cbabb07837cd276c69a9cac8c</t>
+          <t>0x9d32e5f032ba9dc93b95acef35770306b0b442f29190223c082d2e5c1d4b0fe1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.2112</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x087d60f2b64530b4e99ae6c48561d5b3386ce094838052c4e0fec7c1f1178667</t>
+          <t>0x14499f5cbc32bc07affe45ccd6d5961e24e3f27d51409c051daf6c5e5b340ae0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785604435</t>
+          <t>1785610062</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>9.070295</t>
+          <t>5.491124</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x3b6dd2c698f7aff2bed5984985fcb070deff0a89975871642ce3dcfc7d1f75f6</t>
+          <t>0x169247f587f65aaf25de03f170bf7a78ee4415471aee7ad2bf099a73fca25534</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.2112</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x087d60f2b64530b4e99ae6c48561d5b3386ce094838052c4e0fec7c1f1178667</t>
+          <t>0x14499f5cbc32bc07affe45ccd6d5961e24e3f27d51409c051daf6c5e5b340ae0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785604420</t>
+          <t>1785610025</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>25.052154</t>
+          <t>67.266272</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x83586daa8b624bb395a9793e6eeaf39c5af7ecf92aca70fcc997d0161b164af1</t>
+          <t>0x1636c6951aba887bca1708ac218dd9760d6a30e166325f9ca2c555ff64b4a63e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,52 +770,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>22.81</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5288</t>
+          <t>1.3213</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>Primera A</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Alianza FC Valledupar 0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar vs Deportes Tolima</t>
+          <t>Deportivo Pasto vs Rionegro Aguilas</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Deportes Tolima</t>
+          <t>Rionegro Aguilas</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x4ddfc7fb64d3be5c60749a1a51d33f1a0f7a0fdd73b13c70c2475c7c6e5d5e8b</t>
+          <t>0x1d1900b1b04981a9d51d3afa4f9ca96a4687be8dd53a624fad73d1311887eed9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19596461</t>
+          <t>L19596456</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785602079</t>
+          <t>1785609784</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785618300</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>33.777778</t>
+          <t>71.003891</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x84ff211f672e64e5d239f5382404f6df83a2f9b564faf4d9352f9a40a2858896</t>
+          <t>0xe6bce4fd7847619685cae46bf904c43059efb54cbabb07837cd276c69a9cac8c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,52 +882,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19.817</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5263</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>Primera A</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Alianza FC Valledupar 0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar vs Deportes Tolima</t>
+          <t>Deportivo Pasto vs Rionegro Aguilas</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Deportes Tolima</t>
+          <t>Rionegro Aguilas</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x4ddfc7fb64d3be5c60749a1a51d33f1a0f7a0fdd73b13c70c2475c7c6e5d5e8b</t>
+          <t>0x087d60f2b64530b4e99ae6c48561d5b3386ce094838052c4e0fec7c1f1178667</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19596461</t>
+          <t>L19596456</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785600148</t>
+          <t>1785604435</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785618300</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37.657007</t>
+          <t>9.070295</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,31 +979,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xac2cdbb4245f52c679b04de9218642f91f9f0d418f7421c33d5b7419c6453ec1</t>
+          <t>0x3b6dd2c698f7aff2bed5984985fcb070deff0a89975871642ce3dcfc7d1f75f6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23.99956</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.665</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -1011,27 +1019,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar vs Deportes Tolima</t>
+          <t>Deportivo Pasto vs Rionegro Aguilas</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Deportes Tolima</t>
+          <t>Rionegro Aguilas</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xcf149e7edabae12c7cce191667def8c5527e5a2a4a0b1139d7dbc0ee55cb0657</t>
+          <t>0x087d60f2b64530b4e99ae6c48561d5b3386ce094838052c4e0fec7c1f1178667</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19596461</t>
+          <t>L19596456</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1064,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785598651</t>
+          <t>1785604420</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785618300</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>36.089564</t>
+          <t>25.052154</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1091,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x4e6d8aa3987bcfa005261070885a48fd586f27d2bc70935198f0e47d5d57bbc1</t>
+          <t>0x83586daa8b624bb395a9793e6eeaf39c5af7ecf92aca70fcc997d0161b164af1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,22 +1106,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2725</t>
+          <t>1.5288</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Primera A</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Alianza FC Valledupar 0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,27 +1131,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Alianza FC Valledupar vs Deportes Tolima</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x99fd85073e61e4ff2811a42fd3c5860bb029aa8bb2842c318e468f64896ecc5e</t>
+          <t>0x4ddfc7fb64d3be5c60749a1a51d33f1a0f7a0fdd73b13c70c2475c7c6e5d5e8b</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19596461</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1176,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785565485</t>
+          <t>1785602079</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785618300</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>9.321101</t>
+          <t>33.777778</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,7 +1203,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xa1c75ce4ff8b084ebb89ef9c554b972ba868d695f41f84d5d7eba65ab3bf430e</t>
+          <t>0x84ff211f672e64e5d239f5382404f6df83a2f9b564faf4d9352f9a40a2858896</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1210,22 +1218,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19.817</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.5263</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Primera A</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Alianza FC Valledupar 0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1235,27 +1243,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Alianza FC Valledupar vs Deportes Tolima</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x175c82298fd904f82cec6e6df95a6caa5e2925c38ac62b465dc3c16cbe6d7468</t>
+          <t>0x4ddfc7fb64d3be5c60749a1a51d33f1a0f7a0fdd73b13c70c2475c7c6e5d5e8b</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19596461</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1288,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785565483</t>
+          <t>1785600148</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785618300</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>20.460358</t>
+          <t>37.657007</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,7 +1315,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x804741c7cadd40e1de9b46da558e4f8f76822d01b445af10dcb9b394ea6818b4</t>
+          <t>0xac2cdbb4245f52c679b04de9218642f91f9f0d418f7421c33d5b7419c6453ec1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1315,31 +1323,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9.99998</t>
+          <t>23.99956</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.7525</t>
+          <t>1.665</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -1347,27 +1347,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Alianza FC Valledupar vs Deportes Tolima</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Deportes Tolima</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x3461ee17d707212e3a9027bdc8a10f2a6481bbeefaa491f85e9dad2fc6ef04cd</t>
+          <t>0xcf149e7edabae12c7cce191667def8c5527e5a2a4a0b1139d7dbc0ee55cb0657</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19596461</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785565483</t>
+          <t>1785598651</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785618300</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13.28901</t>
+          <t>36.089564</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x7c7a7beca6e326a985496bfa5683eb5fa550e0b516fd6ce073773eb404203a24</t>
+          <t>0x4e6d8aa3987bcfa005261070885a48fd586f27d2bc70935198f0e47d5d57bbc1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1434,22 +1434,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.2725</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF -1</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1459,27 +1459,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF vs Deportivo Pereira</t>
+          <t>CDP Junior FC vs Millonarios</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>CDP Junior FC</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
+          <t>0x99fd85073e61e4ff2811a42fd3c5860bb029aa8bb2842c318e468f64896ecc5e</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19596272</t>
+          <t>L19606649</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1504,17 +1504,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785508565</t>
+          <t>1785565485</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785546000</t>
+          <t>1785633300</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2074.074074</t>
+          <t>9.321101</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1531,12 +1531,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xd193b26f2bd560add82739bdab75d53f792eabeb2448f88b702c3e11effb030c</t>
+          <t>0xa1c75ce4ff8b084ebb89ef9c554b972ba868d695f41f84d5d7eba65ab3bf430e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>999.99999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF -1</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1571,27 +1571,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF vs Deportivo Pereira</t>
+          <t>CDP Junior FC vs Millonarios</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>CDP Junior FC</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
+          <t>0x175c82298fd904f82cec6e6df95a6caa5e2925c38ac62b465dc3c16cbe6d7468</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19596272</t>
+          <t>L19606649</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1616,17 +1616,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785508452</t>
+          <t>1785565483</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785546000</t>
+          <t>1785633300</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1980.198</t>
+          <t>20.460358</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1643,12 +1643,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xdcff50b650be0657ac4bc1268770ca1b1ea0c65c290a0a114d293e00512af266</t>
+          <t>0x804741c7cadd40e1de9b46da558e4f8f76822d01b445af10dcb9b394ea6818b4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1658,22 +1658,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>9.99998</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.7525</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF -1</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF vs Deportivo Pereira</t>
+          <t>CDP Junior FC vs Millonarios</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF</t>
+          <t>CDP Junior FC</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
+          <t>0x3461ee17d707212e3a9027bdc8a10f2a6481bbeefaa491f85e9dad2fc6ef04cd</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19596272</t>
+          <t>L19606649</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1728,17 +1728,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785508288</t>
+          <t>1785565483</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785546000</t>
+          <t>1785633300</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>597.014925</t>
+          <t>13.28901</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xa40848b46172c1286780eed941c034eeb3a03a4e6390b868015e86a64c340cbf</t>
+          <t>0x7c7a7beca6e326a985496bfa5683eb5fa550e0b516fd6ce073773eb404203a24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>906.8</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785508285</t>
+          <t>1785508565</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1804.577114</t>
+          <t>2074.074074</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1867,12 +1867,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x74b91529e11bc9b801aabc69fc095fca7f0d47339dbee7f0423c6e1fe35b3c56</t>
+          <t>0xd193b26f2bd560add82739bdab75d53f792eabeb2448f88b702c3e11effb030c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x1366520A029cac333db38288dEeC1cDB6805FE20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>999.99999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785508244</t>
+          <t>1785508452</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>597.014925</t>
+          <t>1980.198</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1979,12 +1979,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xedba5ec6631e3639ff5145bb305ece20e8b3069364c2fe3934ad13a18e2004f2</t>
+          <t>0xdcff50b650be0657ac4bc1268770ca1b1ea0c65c290a0a114d293e00512af266</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1994,22 +1994,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.2725</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Fortaleza CEIF -1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2019,27 +2019,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785459663</t>
+          <t>1785508288</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>68.697248</t>
+          <t>597.014925</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2091,31 +2091,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xa9091dfd45d7760564c0997da3a60bab168f54643ab31141aca0ab8e9ec81033</t>
+          <t>0xa40848b46172c1286780eed941c034eeb3a03a4e6390b868015e86a64c340cbf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>141.53</t>
+          <t>906.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF -1</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -2123,27 +2131,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2168,17 +2176,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785459106</t>
+          <t>1785508285</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>288.101781</t>
+          <t>1804.577114</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2195,23 +2203,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x70dfc6080b5ce53089fea0fe9e58e8db2d467e73911ac1c24f0e3132eeff93ff</t>
+          <t>0x74b91529e11bc9b801aabc69fc095fca7f0d47339dbee7f0423c6e1fe35b3c56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>141.53</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2219,7 +2231,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF -1</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -2227,27 +2243,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
+          <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Atlético Bucaramanga</t>
+          <t>Fortaleza CEIF</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x49b3b490d08054a50d868ebab048f8663a65751eca4f638a105e18ac68762570</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19614187</t>
+          <t>L19596272</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2272,17 +2288,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785459106</t>
+          <t>1785508244</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785546000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>288.101781</t>
+          <t>597.014925</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2299,31 +2315,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xda5a2ca0728ab585a3a0a417b6b9bc3201516e60647947d6c517fe5aa3b61048</t>
+          <t>0xedba5ec6631e3639ff5145bb305ece20e8b3069364c2fe3934ad13a18e2004f2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6.485</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.2725</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -2346,7 +2370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2376,7 +2400,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785459011</t>
+          <t>1785459663</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2386,7 +2410,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13.167513</t>
+          <t>68.697248</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2403,23 +2427,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x0331bf2d5e4c5647823514fbecd4538f8b83f08eca73864d773e7766b093fb2a</t>
+          <t>0xa9091dfd45d7760564c0997da3a60bab168f54643ab31141aca0ab8e9ec81033</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6.485</t>
+          <t>141.53</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2480,7 +2504,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785459011</t>
+          <t>1785459106</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2490,7 +2514,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>13.167513</t>
+          <t>288.101781</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2507,18 +2531,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x7c7ef31eaf86810e695207fb33fbd17c8a9667464f034b54067116201439a051</t>
+          <t>0x70dfc6080b5ce53089fea0fe9e58e8db2d467e73911ac1c24f0e3132eeff93ff</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>141.53</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2528,7 +2552,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2554,7 +2578,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2584,7 +2608,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785458828</t>
+          <t>1785459106</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2594,7 +2618,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>13.964377</t>
+          <t>288.101781</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2611,7 +2635,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x4bae0ce9888d9df37c25c3bd52c2cef2988011ef9500547215ff3c01a8d9ade3</t>
+          <t>0xda5a2ca0728ab585a3a0a417b6b9bc3201516e60647947d6c517fe5aa3b61048</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2622,12 +2646,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>6.485</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2688,7 +2712,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785458828</t>
+          <t>1785459011</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2698,7 +2722,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>13.964377</t>
+          <t>13.167513</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2715,7 +2739,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xf11827477b399686fb93d667a743105e76379dbd2b6ac26fe365b2efa2755088</t>
+          <t>0x0331bf2d5e4c5647823514fbecd4538f8b83f08eca73864d773e7766b093fb2a</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2726,17 +2750,17 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>55.54</t>
+          <t>6.485</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2762,7 +2786,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2792,7 +2816,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785458766</t>
+          <t>1785459011</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2802,7 +2826,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>113.058524</t>
+          <t>13.167513</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2819,7 +2843,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xf172f33c4c2b23605bea3d982f0b82c718d3cccf29fa086a1fbcefb977260877</t>
+          <t>0x7c7ef31eaf86810e695207fb33fbd17c8a9667464f034b54067116201439a051</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2830,7 +2854,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>55.54</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2896,7 +2920,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785458765</t>
+          <t>1785458828</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2906,7 +2930,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>113.058524</t>
+          <t>13.964377</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2923,7 +2947,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x770626413b7eb60a07b8e7cb17c67cedae414407b96deb76fd5c4807ea3ab23b</t>
+          <t>0x4bae0ce9888d9df37c25c3bd52c2cef2988011ef9500547215ff3c01a8d9ade3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2934,17 +2958,17 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>35.175</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2970,7 +2994,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3000,7 +3024,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785458648</t>
+          <t>1785458828</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3010,7 +3034,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>71.785714</t>
+          <t>13.964377</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3027,7 +3051,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x420fca3536f3ce2e4be9cfdac1490c3e4a1c8f41c1bd5b62c154f6949a0250d6</t>
+          <t>0xf11827477b399686fb93d667a743105e76379dbd2b6ac26fe365b2efa2755088</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3038,12 +3062,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>35.175</t>
+          <t>55.54</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3104,7 +3128,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785458648</t>
+          <t>1785458766</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3114,7 +3138,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>71.785714</t>
+          <t>113.058524</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3131,7 +3155,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xdb01c85c09482b9001bcf21790a6d40494a3a5aaf4f8d5bd2884e25499a54a65</t>
+          <t>0xf172f33c4c2b23605bea3d982f0b82c718d3cccf29fa086a1fbcefb977260877</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3142,12 +3166,12 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>12.025</t>
+          <t>55.54</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3208,7 +3232,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785458515</t>
+          <t>1785458765</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3218,7 +3242,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>24.416244</t>
+          <t>113.058524</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3235,7 +3259,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x5ecc4ae58c7b78276b0defbe103a322d68a770b3df079f300e5c69c2b4731021</t>
+          <t>0x770626413b7eb60a07b8e7cb17c67cedae414407b96deb76fd5c4807ea3ab23b</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3246,17 +3270,17 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>12.025</t>
+          <t>35.175</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3282,7 +3306,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3312,7 +3336,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785458515</t>
+          <t>1785458648</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3322,7 +3346,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>24.416244</t>
+          <t>71.785714</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3339,23 +3363,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xec7f090351108b7b958a5c4fb3783282609cba12a18c5d155c1f5534aef15888</t>
+          <t>0x420fca3536f3ce2e4be9cfdac1490c3e4a1c8f41c1bd5b62c154f6949a0250d6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1440.5</t>
+          <t>35.175</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3416,7 +3440,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785458317</t>
+          <t>1785458648</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3426,7 +3450,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2932.315522</t>
+          <t>71.785714</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3443,23 +3467,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xd8cf4f50c442be3b22b3347558a79fd346b09cc1ef8e9b148523105c1d6f374a</t>
+          <t>0xdb01c85c09482b9001bcf21790a6d40494a3a5aaf4f8d5bd2884e25499a54a65</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1440.5</t>
+          <t>12.025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4912</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3520,7 +3544,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785458316</t>
+          <t>1785458515</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3530,7 +3554,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2932.315522</t>
+          <t>24.416244</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3547,39 +3571,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x6227261e94b21a2814a481af754aa21193c650ab023cebd08d07fdd92c227638</t>
+          <t>0x5ecc4ae58c7b78276b0defbe103a322d68a770b3df079f300e5c69c2b4731021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>56.97</t>
+          <t>12.025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.2725</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -3602,7 +3618,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3632,7 +3648,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785457967</t>
+          <t>1785458515</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3642,7 +3658,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>209.06422</t>
+          <t>24.416244</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3659,28 +3675,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xe210f9e86e0bb9e0dd548ab19bdfc825697ddbd94a1f44c6b09e392508136305</t>
+          <t>0xec7f090351108b7b958a5c4fb3783282609cba12a18c5d155c1f5534aef15888</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>33.88744</t>
+          <t>1440.5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.7075</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3706,7 +3722,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3736,7 +3752,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785457812</t>
+          <t>1785458317</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3746,7 +3762,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>47.897442</t>
+          <t>2932.315522</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3763,23 +3779,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x357158ee54a7261c9a3de5193f26c50059ecf3942905b81e23da928f3597b963</t>
+          <t>0xd8cf4f50c442be3b22b3347558a79fd346b09cc1ef8e9b148523105c1d6f374a</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>310.405</t>
+          <t>1440.5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.4912</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3840,7 +3856,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785457812</t>
+          <t>1785458316</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3850,7 +3866,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>627.080808</t>
+          <t>2932.315522</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3867,31 +3883,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x07d4c22db9e039aaab83659c51b2c610ff2420310c4aa2f6fa5ee9aaa5df5738</t>
+          <t>0x6227261e94b21a2814a481af754aa21193c650ab023cebd08d07fdd92c227638</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>310.405</t>
+          <t>56.97</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1.2725</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -3914,7 +3938,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x95c5e9ab93e40d485bbf395fd600cc7c21f29ed7e05089b30656e50317c9f5d8</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3944,7 +3968,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785457812</t>
+          <t>1785457967</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3954,7 +3978,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>627.080808</t>
+          <t>209.06422</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3971,28 +3995,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x965925cb75ca17bc44d1270de6e7856136b50e2ba8df869b8ba43a9edfa8cd2c</t>
+          <t>0xe210f9e86e0bb9e0dd548ab19bdfc825697ddbd94a1f44c6b09e392508136305</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>111.49999</t>
+          <t>33.88744</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.7075</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4018,7 +4042,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4048,7 +4072,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785457798</t>
+          <t>1785457812</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4058,7 +4082,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>229.896887</t>
+          <t>47.897442</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4075,23 +4099,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x11cdcc8f35a6869fb42fc42979f00e55e1793e1eaf537612d53ad40413422d94</t>
+          <t>0x357158ee54a7261c9a3de5193f26c50059ecf3942905b81e23da928f3597b963</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>111.49999</t>
+          <t>310.405</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4152,7 +4176,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785457797</t>
+          <t>1785457812</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4162,7 +4186,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>229.896887</t>
+          <t>627.080808</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4179,23 +4203,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xb08a5fa81a7996a995791b3f412a72d7c00869095f73062c91c21ec7d19936a7</t>
+          <t>0x07d4c22db9e039aaab83659c51b2c610ff2420310c4aa2f6fa5ee9aaa5df5738</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>310.405</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.485</t>
+          <t>1.495</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4256,7 +4280,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785457480</t>
+          <t>1785457812</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4266,7 +4290,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>459.793814</t>
+          <t>627.080808</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4283,18 +4307,18 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xcd0842e0ce38af317ba18078937aa447779373f330d888eda16082ee857c491b</t>
+          <t>0x965925cb75ca17bc44d1270de6e7856136b50e2ba8df869b8ba43a9edfa8cd2c</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>111.49999</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4304,7 +4328,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4330,7 +4354,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4360,7 +4384,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785457479</t>
+          <t>1785457798</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4370,7 +4394,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>459.793814</t>
+          <t>229.896887</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4387,18 +4411,18 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x298fa2b8022c9fc657efcae03bbf1c76286c06ada5e405c0b8c01f690927ea9d</t>
+          <t>0x11cdcc8f35a6869fb42fc42979f00e55e1793e1eaf537612d53ad40413422d94</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x2Bd56fa0D7b1Add3639Ee23f32A2947576924f15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>280.25</t>
+          <t>111.49999</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4408,7 +4432,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -4434,7 +4458,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4464,7 +4488,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785457343</t>
+          <t>1785457797</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4474,7 +4498,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>577.835052</t>
+          <t>229.896887</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4491,18 +4515,18 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x849609d6471964d5175246b6bc924306468693f7d1aec2da18390bda2d54e0ad</t>
+          <t>0xb08a5fa81a7996a995791b3f412a72d7c00869095f73062c91c21ec7d19936a7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>280.25</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4512,7 +4536,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4538,7 +4562,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4568,7 +4592,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785457342</t>
+          <t>1785457480</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4578,7 +4602,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>577.835052</t>
+          <t>459.793814</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4595,18 +4619,18 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xbb37e766b7f859769dd38edd2c0b7223eed00c663e6d49a7bfab098f486c206b</t>
+          <t>0xcd0842e0ce38af317ba18078937aa447779373f330d888eda16082ee857c491b</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x601fEe613FbdD8A867DEFF5585b53EeDE11060f2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4672,7 +4696,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785457307</t>
+          <t>1785457479</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4682,7 +4706,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>309.278351</t>
+          <t>459.793814</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4699,18 +4723,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x8f0dbefc5a409af568cf2a038c3e5e0195adaae1692daaf1ec7d82108ff43db8</t>
+          <t>0x298fa2b8022c9fc657efcae03bbf1c76286c06ada5e405c0b8c01f690927ea9d</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>280.25</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4776,7 +4800,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785457307</t>
+          <t>1785457343</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4786,7 +4810,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>309.278351</t>
+          <t>577.835052</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4803,28 +4827,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x9b20bc474ab348aac134c9be069f670928a6c80a3155e27f3467f12716165c53</t>
+          <t>0x849609d6471964d5175246b6bc924306468693f7d1aec2da18390bda2d54e0ad</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>280.25</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4850,7 +4874,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4880,7 +4904,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785457201</t>
+          <t>1785457342</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4890,7 +4914,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>510.769231</t>
+          <t>577.835052</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4907,23 +4931,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x3dda88350d6105418404aee1ac185f1858e87b0aba5134695793d721acf1d81d</t>
+          <t>0xbb37e766b7f859769dd38edd2c0b7223eed00c663e6d49a7bfab098f486c206b</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4984,7 +5008,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785457201</t>
+          <t>1785457307</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4994,7 +5018,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>510.769231</t>
+          <t>309.278351</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5011,7 +5035,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xee9612e6509257c9ad940ec42c374586652e12c5853e386c48508431fbe76d05</t>
+          <t>0x8f0dbefc5a409af568cf2a038c3e5e0195adaae1692daaf1ec7d82108ff43db8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5027,7 +5051,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.485</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5088,7 +5112,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785456804</t>
+          <t>1785457307</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5098,7 +5122,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>307.692308</t>
+          <t>309.278351</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5115,18 +5139,18 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x6ba83cbce2c597c47ad2be6ba26f984375bb5e0a7536df8e0c8b906cdd3cf4b5</t>
+          <t>0x9b20bc474ab348aac134c9be069f670928a6c80a3155e27f3467f12716165c53</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5136,7 +5160,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5162,7 +5186,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5192,7 +5216,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785456804</t>
+          <t>1785457201</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5202,7 +5226,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>307.692308</t>
+          <t>510.769231</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5219,28 +5243,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x8fd96b8c3d361ca4f5d4c858af827e49ded210592392fcd9b074b2a925deaca5</t>
+          <t>0x3dda88350d6105418404aee1ac185f1858e87b0aba5134695793d721acf1d81d</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xfCDe5662b9dE9A9E78aAB9809c34535134EA6cF4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>249</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5266,7 +5290,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5296,7 +5320,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785456147</t>
+          <t>1785457201</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5306,7 +5330,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>58.890756</t>
+          <t>510.769231</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5323,28 +5347,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x0d8a3334c7809cd2635630f68c141dd8605f414e3fbfb296be4eac2929105fda</t>
+          <t>0xee9612e6509257c9ad940ec42c374586652e12c5853e386c48508431fbe76d05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5370,7 +5394,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5400,7 +5424,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785456119</t>
+          <t>1785456804</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5410,7 +5434,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>58.890756</t>
+          <t>307.692308</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5427,28 +5451,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xda8af1defc8a29c16e0370161d4a270c766a68fd83aaaeabab9e4378a0673c8d</t>
+          <t>0x6ba83cbce2c597c47ad2be6ba26f984375bb5e0a7536df8e0c8b906cdd3cf4b5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>14.76</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -5474,7 +5498,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+          <t>0xead536ea81eb4df17f33676a7babd4100380d9cf00e04d8938e7b6c8d9b5a03d</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5504,7 +5528,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785456113</t>
+          <t>1785456804</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5514,7 +5538,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>307.692308</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5531,28 +5555,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x6455a52d539e6161d9660f2b64423ad8c44b72329f3184934b7abf12459e522b</t>
+          <t>0x8fd96b8c3d361ca4f5d4c858af827e49ded210592392fcd9b074b2a925deaca5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5578,7 +5602,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5608,7 +5632,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785456018</t>
+          <t>1785456147</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5618,7 +5642,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>5.333333</t>
+          <t>58.890756</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5635,28 +5659,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xf8952a0d91c993a93b0aa47a324ed3d061daa3d53d2a7d88bb539b259c373f92</t>
+          <t>0x0d8a3334c7809cd2635630f68c141dd8605f414e3fbfb296be4eac2929105fda</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5682,7 +5706,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
+          <t>0xd090d04f2cc1006a7bb8aa22e3bc8f2c83417372544e7eb6587cfa4948423bac</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5712,7 +5736,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785456003</t>
+          <t>1785456119</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5722,7 +5746,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>5.209877</t>
+          <t>58.890756</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5739,7 +5763,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x999afcdc39345ad0d2e993258d3826f21e43481b2950dcb0f638f2992ac4e4f6</t>
+          <t>0xda8af1defc8a29c16e0370161d4a270c766a68fd83aaaeabab9e4378a0673c8d</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5747,31 +5771,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.9244</t>
+          <t>14.76</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5794,7 +5810,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5824,7 +5840,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785454208</t>
+          <t>1785456113</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5834,7 +5850,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2.88875</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5851,7 +5867,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xf482d08d1fd572eed4c342d8ff10a66ebe3280fdda896e40e465f342e911ccd5</t>
+          <t>0x6455a52d539e6161d9660f2b64423ad8c44b72329f3184934b7abf12459e522b</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5859,31 +5875,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>12.52</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -5906,7 +5914,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5936,7 +5944,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785454207</t>
+          <t>1785456018</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5946,7 +5954,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>40.064</t>
+          <t>5.333333</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5963,7 +5971,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xee4006c4eddaff028b23356cb7de9590b5936ce913b2d1805c50154d5126e6e0</t>
+          <t>0xf8952a0d91c993a93b0aa47a324ed3d061daa3d53d2a7d88bb539b259c373f92</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5971,31 +5979,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.3125</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
+          <t>0xaeed8e60f578170a4a726abeb65350820daa40a201742255fd784e3145b94300</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785454207</t>
+          <t>1785456003</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5.209877</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6075,31 +6075,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x767f70e59b8e41cdfebda1051f2fa906a012de9bfa55942c59f4f2146ac6192f</t>
+          <t>0x999afcdc39345ad0d2e993258d3826f21e43481b2950dcb0f638f2992ac4e4f6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x1ea5530Db70D5dA696cC1038be611Be53Db5C60F</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>0.9244</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -6122,7 +6130,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6152,7 +6160,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785440016</t>
+          <t>1785454208</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6162,7 +6170,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>444.239631</t>
+          <t>2.88875</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6179,7 +6187,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x407971887685061312685cb0b7f5ef9ed6261d2f1b2d1f09c45aa4eae0a05e25</t>
+          <t>0xf482d08d1fd572eed4c342d8ff10a66ebe3280fdda896e40e465f342e911ccd5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6187,23 +6195,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3.57999</t>
+          <t>12.52</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -6226,7 +6242,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6256,7 +6272,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785434777</t>
+          <t>1785454207</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6266,7 +6282,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>6.59906</t>
+          <t>40.064</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6283,31 +6299,39 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
+          <t>0xee4006c4eddaff028b23356cb7de9590b5936ce913b2d1805c50154d5126e6e0</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>60.05998</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.7575</t>
+          <t>1.3125</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga -1.5</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Primera A</t>
@@ -6315,27 +6339,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CDP Junior FC vs Millonarios</t>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>CDP Junior FC</t>
+          <t>Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+          <t>0x6b991bef49ab77e5b1ce2c3988216602f2686ccc6b52c25f1e5e96ed45f0e087</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19606649</t>
+          <t>L19614187</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6360,17 +6384,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785400533</t>
+          <t>1785454207</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1785633300</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>79.287102</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6387,54 +6411,46 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+          <t>0x767f70e59b8e41cdfebda1051f2fa906a012de9bfa55942c59f4f2146ac6192f</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x1ea5530Db70D5dA696cC1038be611Be53Db5C60F</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.6637</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>Atlético Bucaramanga</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Primera A</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga vs Llaneros FC</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Atlético Bucaramanga</t>
-        </is>
-      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>Llaneros FC</t>
@@ -6442,7 +6458,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6472,7 +6488,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785344668</t>
+          <t>1785440016</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6482,7 +6498,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1.506591</t>
+          <t>444.239631</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6499,110 +6515,430 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>0x407971887685061312685cb0b7f5ef9ed6261d2f1b2d1f09c45aa4eae0a05e25</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3.57999</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.5425</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0x481fdaa2a20c002d515f3c43eac07f52063302592153594bc8cb3d995852a008</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1785434777</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>6.59906</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0x7329421797dc603c2125293bb4d7a5bfcff5a6ef4e85c5df6823893cb97e17ee</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>60.05998</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.7575</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>CDP Junior FC vs Millonarios</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>CDP Junior FC</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0x0793e576da59b70aa8ea4c5fb634c02f46858b912ecd6a02f91f6ebbaa986be7</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19606649</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1785400533</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1785633300</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>79.287102</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0x9ff1fda59e1de553a293f3669eef33f243c577ad387b1abf6cbe9347473b44c6</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.6637</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Primera A</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0x0a67b48214c191d8392e1d2d3f46113bbde830da36a1ff74ffb1f181c08e506b</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19614187</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1785344668</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1.506591</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>0xb99da8b648376c357d13a6060e6f4dc2ae7491c558b543e4c668392cdfe2e5bd</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>0.99999</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>1.6987</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Primera A</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>Fortaleza CEIF vs Deportivo Pereira</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Fortaleza CEIF</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>Deportivo Pereira</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>0xd09cb30bf0c8317660cdcbbfc8ea542253305047aabd0fa7acee0ff117d36274</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>L19596272</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
         <is>
           <t>1785344544</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>1785546000</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>1.431113</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
